--- a/nms_multibagger_candidates_midcap_plus.xlsx
+++ b/nms_multibagger_candidates_midcap_plus.xlsx
@@ -6029,7 +6029,7 @@
         </is>
       </c>
       <c r="L81" s="22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M81" s="22" t="n">
         <v>3</v>
@@ -13021,7 +13021,7 @@
         </is>
       </c>
       <c r="L189" s="22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M189" s="22" t="n">
         <v>3</v>
@@ -21557,14 +21557,14 @@
         </is>
       </c>
       <c r="L96" s="22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M96" s="22" t="n">
         <v>3</v>
       </c>
       <c r="N96" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, DeadOption, OakDeepValue, XR-Asse</t>
+          <t>NarrativeLag, FixedCost+DemandShock, DeadOption, OakDeepValue, Cundill</t>
         </is>
       </c>
       <c r="O96" s="24" t="n">
@@ -23950,14 +23950,14 @@
         </is>
       </c>
       <c r="L133" s="22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M133" s="22" t="n">
         <v>3</v>
       </c>
       <c r="N133" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, DeadOption, XR-LatentInflectionFl</t>
+          <t>NarrativeLag, FixedCost+DemandShock, DeadOption, Cundill-CrisisRecover</t>
         </is>
       </c>
       <c r="O133" s="24" t="n">
@@ -25632,7 +25632,7 @@
         </is>
       </c>
       <c r="L159" s="22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M159" s="22" t="n">
         <v>5</v>
@@ -27838,14 +27838,14 @@
         </is>
       </c>
       <c r="L193" s="22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M193" s="22" t="n">
         <v>4</v>
       </c>
       <c r="N193" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, KPIThreshold, CapitalReturner, Fo</t>
+          <t>NarrativeLag, FixedCost+DemandShock, KPIThreshold, CapitalReturner, Cu</t>
         </is>
       </c>
       <c r="O193" s="24" t="n">
@@ -58512,14 +58512,14 @@
         </is>
       </c>
       <c r="L452" s="22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M452" s="22" t="n">
         <v>1</v>
       </c>
       <c r="N452" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, NetCashReturner, StrongCoverage, HiddenAssets-Overcap, F</t>
+          <t>NarrativeLag, NetCashReturner, StrongCoverage, Cundill-CrisisRecovery,</t>
         </is>
       </c>
       <c r="O452" s="24" t="n">
@@ -58642,7 +58642,7 @@
         </is>
       </c>
       <c r="L454" s="22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M454" s="22" t="n">
         <v>2</v>

--- a/nms_multibagger_candidates_midcap_plus.xlsx
+++ b/nms_multibagger_candidates_midcap_plus.xlsx
@@ -14,8 +14,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CANDIDATE_Top500" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'STRICT'!$B$3:$P$266</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'STRONG'!$B$3:$P$269</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'STRICT'!$B$3:$P$267</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'STRONG'!$B$3:$P$268</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'CANDIDATE_Top500'!$B$3:$P$503</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -658,7 +658,7 @@
     <row r="9" ht="22" customHeight="1">
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>This shortlist filters the 4,865 multibagger candidates in the NMS sub-universe (mcap &lt; ~$2B, RED-verdicted names excluded). Each name is assigned a conviction tier based on its archetype-count, inflection-cluster density and asymmetry score. STRICT (263) = 5+ archetypes firing AND 3+ inflection signals AND asymmetry &gt;= 0.40. STRONG (266) = 3+ archetypes AND 3+ inflection signals AND asymmetry &gt;= 0.35. CANDIDATE (4336) = the broader funnel - 3+ archetypes or 4+ inflection signals at asymmetry &gt;= 0.35. (Multi-archetype gates are calibrated to the current 69-archetype taxonomy.) Within each tier, names are ranked by confirmed entry-today asymmetry (asymmetry_score x qual_multiplier x post-rally factor x confirmation multiplier (1 + 0.20 x confirm_overall + 0.10 x buyback_score)).</t>
+          <t>This shortlist filters the 4,865 multibagger candidates in the NMS sub-universe (mcap &lt; ~$2B, RED-verdicted names excluded). Each name is assigned a conviction tier based on its archetype-count, inflection-cluster density and asymmetry score. STRICT (264) = 5+ archetypes firing AND 3+ inflection signals AND asymmetry &gt;= 0.40. STRONG (265) = 3+ archetypes AND 3+ inflection signals AND asymmetry &gt;= 0.35. CANDIDATE (4336) = the broader funnel - 3+ archetypes or 4+ inflection signals at asymmetry &gt;= 0.35. (Multi-archetype gates are calibrated to the current 69-archetype taxonomy.) Within each tier, names are ranked by confirmed entry-today asymmetry (asymmetry_score x qual_multiplier x post-rally factor x confirmation multiplier (1 + 0.20 x confirm_overall + 0.10 x buyback_score)).</t>
         </is>
       </c>
     </row>
@@ -702,12 +702,12 @@
     <row r="20" ht="30" customHeight="1">
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>264</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>265</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -882,7 +882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P266"/>
+  <dimension ref="A1:P267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -907,7 +907,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRICT — high conviction — 263 names</t>
+          <t xml:space="preserve">  STRICT — high conviction — 264 names</t>
         </is>
       </c>
       <c r="B1" s="11" t="n"/>
@@ -3636,7 +3636,7 @@
         </is>
       </c>
       <c r="L44" s="22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M44" s="22" t="n">
         <v>3</v>
@@ -13179,12 +13179,12 @@
       </c>
       <c r="D192" s="18" t="inlineStr">
         <is>
-          <t>PIFMF</t>
+          <t>UMICF</t>
         </is>
       </c>
       <c r="E192" s="19" t="inlineStr">
         <is>
-          <t>PT Indofood Sukses Makmur Tbk</t>
+          <t>Umicore SA</t>
         </is>
       </c>
       <c r="F192" s="26" t="inlineStr">
@@ -13194,12 +13194,12 @@
       </c>
       <c r="G192" s="21" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H192" s="21" t="inlineStr">
         <is>
-          <t>Food &amp; Staples Retailing</t>
+          <t>Construction &amp; Engineering</t>
         </is>
       </c>
       <c r="I192" s="16" t="inlineStr">
@@ -13208,7 +13208,7 @@
         </is>
       </c>
       <c r="J192" s="22" t="n">
-        <v>3599974656</v>
+        <v>6209218048</v>
       </c>
       <c r="K192" s="25" t="inlineStr">
         <is>
@@ -13216,21 +13216,21 @@
         </is>
       </c>
       <c r="L192" s="22" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M192" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N192" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, CapitalDiscipline, OwnerOperator, MidCapGARP, LynchEV-GY</t>
+          <t>FixedCost+DemandShock, KPIThreshold, MidCapGARP, BAB-Becoming, LynchPE</t>
         </is>
       </c>
       <c r="O192" s="24" t="n">
-        <v>0.425402653358671</v>
+        <v>0.4333506010109346</v>
       </c>
       <c r="P192" s="24" t="n">
-        <v>0.44183961</v>
+        <v>0.441537726</v>
       </c>
     </row>
     <row r="193" ht="16" customHeight="1">
@@ -13244,27 +13244,27 @@
       </c>
       <c r="D193" s="18" t="inlineStr">
         <is>
-          <t>UMICF</t>
+          <t>603659.SS</t>
         </is>
       </c>
       <c r="E193" s="19" t="inlineStr">
         <is>
-          <t>Umicore SA</t>
+          <t>Shanghai Putailai New Energy Technology Co., Ltd.</t>
         </is>
       </c>
       <c r="F193" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G193" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H193" s="21" t="inlineStr">
         <is>
-          <t>Construction &amp; Engineering</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="I193" s="16" t="inlineStr">
@@ -13273,7 +13273,7 @@
         </is>
       </c>
       <c r="J193" s="22" t="n">
-        <v>6209218048</v>
+        <v>6775944979.991455</v>
       </c>
       <c r="K193" s="25" t="inlineStr">
         <is>
@@ -13281,21 +13281,21 @@
         </is>
       </c>
       <c r="L193" s="22" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="M193" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N193" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, KPIThreshold, MidCapGARP, BAB-Becoming, LynchPE</t>
+          <t>NarrativeLag, FixedCost+DemandShock, DeadOption, KPIThreshold, MidCapG</t>
         </is>
       </c>
       <c r="O193" s="24" t="n">
-        <v>0.4333506010109346</v>
+        <v>0.4185875724253831</v>
       </c>
       <c r="P193" s="24" t="n">
-        <v>0.441537726</v>
+        <v>0.4413756964</v>
       </c>
     </row>
     <row r="194" ht="16" customHeight="1">
@@ -13309,27 +13309,27 @@
       </c>
       <c r="D194" s="18" t="inlineStr">
         <is>
-          <t>603659.SS</t>
+          <t>IHS</t>
         </is>
       </c>
       <c r="E194" s="19" t="inlineStr">
         <is>
-          <t>Shanghai Putailai New Energy Technology Co., Ltd.</t>
+          <t>IHS Holding Limited Ordinary Shares</t>
         </is>
       </c>
       <c r="F194" s="26" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G194" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="H194" s="21" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Diversified Telecommunication Services</t>
         </is>
       </c>
       <c r="I194" s="16" t="inlineStr">
@@ -13338,7 +13338,7 @@
         </is>
       </c>
       <c r="J194" s="22" t="n">
-        <v>6775944979.991455</v>
+        <v>2865746176</v>
       </c>
       <c r="K194" s="25" t="inlineStr">
         <is>
@@ -13346,21 +13346,21 @@
         </is>
       </c>
       <c r="L194" s="22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M194" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N194" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, DeadOption, KPIThreshold, MidCapG</t>
+          <t>KPIThreshold, QuietCompounder, MidCapGARP, LynchEV-GY, Forensic-Unders</t>
         </is>
       </c>
       <c r="O194" s="24" t="n">
-        <v>0.4185875724253831</v>
+        <v>0.4081869342601544</v>
       </c>
       <c r="P194" s="24" t="n">
-        <v>0.4413756964</v>
+        <v>0.4408415999999999</v>
       </c>
     </row>
     <row r="195" ht="16" customHeight="1">
@@ -13374,27 +13374,27 @@
       </c>
       <c r="D195" s="18" t="inlineStr">
         <is>
-          <t>IHS</t>
+          <t>PIFMF</t>
         </is>
       </c>
       <c r="E195" s="19" t="inlineStr">
         <is>
-          <t>IHS Holding Limited Ordinary Shares</t>
+          <t>PT Indofood Sukses Makmur Tbk</t>
         </is>
       </c>
       <c r="F195" s="26" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G195" s="21" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="H195" s="21" t="inlineStr">
         <is>
-          <t>Diversified Telecommunication Services</t>
+          <t>Food &amp; Staples Retailing</t>
         </is>
       </c>
       <c r="I195" s="16" t="inlineStr">
@@ -13403,7 +13403,7 @@
         </is>
       </c>
       <c r="J195" s="22" t="n">
-        <v>2865746176</v>
+        <v>3599974656</v>
       </c>
       <c r="K195" s="25" t="inlineStr">
         <is>
@@ -13411,21 +13411,21 @@
         </is>
       </c>
       <c r="L195" s="22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M195" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N195" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, QuietCompounder, MidCapGARP, LynchEV-GY, Forensic-Unders</t>
+          <t>NarrativeLag, CapitalDiscipline, OwnerOperator, MidCapGARP, LynchEV-GY</t>
         </is>
       </c>
       <c r="O195" s="24" t="n">
-        <v>0.4081869342601544</v>
+        <v>0.425402653358671</v>
       </c>
       <c r="P195" s="24" t="n">
-        <v>0.4408415999999999</v>
+        <v>0.4405160376</v>
       </c>
     </row>
     <row r="196" ht="16" customHeight="1">
@@ -15869,7 +15869,7 @@
         </is>
       </c>
       <c r="L233" s="22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M233" s="22" t="n">
         <v>4</v>
@@ -17774,12 +17774,12 @@
       </c>
       <c r="D263" s="18" t="inlineStr">
         <is>
-          <t>TBLMF</t>
+          <t>TSUSF</t>
         </is>
       </c>
       <c r="E263" s="19" t="inlineStr">
         <is>
-          <t>Tiger Brands Limited</t>
+          <t>Tsuruha Holdings Inc.</t>
         </is>
       </c>
       <c r="F263" s="26" t="inlineStr">
@@ -17789,12 +17789,12 @@
       </c>
       <c r="G263" s="21" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="H263" s="21" t="inlineStr">
         <is>
-          <t>Food &amp; Staples Retailing</t>
+          <t>Pharmaceuticals</t>
         </is>
       </c>
       <c r="I263" s="16" t="inlineStr">
@@ -17803,7 +17803,7 @@
         </is>
       </c>
       <c r="J263" s="22" t="n">
-        <v>2396052992</v>
+        <v>7815836672</v>
       </c>
       <c r="K263" s="25" t="inlineStr">
         <is>
@@ -17811,21 +17811,21 @@
         </is>
       </c>
       <c r="L263" s="22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M263" s="22" t="n">
         <v>3</v>
       </c>
       <c r="N263" s="21" t="inlineStr">
         <is>
-          <t>MidCapGARP, BalanceSheetReturn, NetCashReturner, Kullamagi-Breakout, S</t>
+          <t>Weinstein-Stage2, LynchEV-GY, XR-PeerMarginGap, ExceptionalEVSG, TenBa</t>
         </is>
       </c>
       <c r="O263" s="24" t="n">
-        <v>0.5042037564565361</v>
+        <v>0.5803731904418854</v>
       </c>
       <c r="P263" s="24" t="n">
-        <v>0.213459288</v>
+        <v>0.239856232</v>
       </c>
     </row>
     <row r="264" ht="16" customHeight="1">
@@ -17839,27 +17839,27 @@
       </c>
       <c r="D264" s="18" t="inlineStr">
         <is>
-          <t>3081.TWO</t>
+          <t>TBLMF</t>
         </is>
       </c>
       <c r="E264" s="19" t="inlineStr">
         <is>
-          <t>LandMark Optoelectronics Corporation</t>
+          <t>Tiger Brands Limited</t>
         </is>
       </c>
       <c r="F264" s="26" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G264" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="H264" s="21" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Semiconductor Equipment</t>
+          <t>Food &amp; Staples Retailing</t>
         </is>
       </c>
       <c r="I264" s="16" t="inlineStr">
@@ -17868,7 +17868,7 @@
         </is>
       </c>
       <c r="J264" s="22" t="n">
-        <v>8234829099.417403</v>
+        <v>2396052992</v>
       </c>
       <c r="K264" s="25" t="inlineStr">
         <is>
@@ -17883,14 +17883,14 @@
       </c>
       <c r="N264" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, ONeil-CANSLIM, Kullamagi-Breakout, StrongCoverage, XR-GA</t>
+          <t>MidCapGARP, BalanceSheetReturn, NetCashReturner, Kullamagi-Breakout, S</t>
         </is>
       </c>
       <c r="O264" s="24" t="n">
-        <v>0.4594681108543432</v>
+        <v>0.5042037564565361</v>
       </c>
       <c r="P264" s="24" t="n">
-        <v>0.2039989197</v>
+        <v>0.213459288</v>
       </c>
     </row>
     <row r="265" ht="16" customHeight="1">
@@ -17904,27 +17904,27 @@
       </c>
       <c r="D265" s="18" t="inlineStr">
         <is>
-          <t>PTGCF</t>
+          <t>3081.TWO</t>
         </is>
       </c>
       <c r="E265" s="19" t="inlineStr">
         <is>
-          <t>PTT Global Chemical Public Company Limited</t>
+          <t>LandMark Optoelectronics Corporation</t>
         </is>
       </c>
       <c r="F265" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G265" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H265" s="21" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Semiconductors &amp; Semiconductor Equipment</t>
         </is>
       </c>
       <c r="I265" s="16" t="inlineStr">
@@ -17933,7 +17933,7 @@
         </is>
       </c>
       <c r="J265" s="22" t="n">
-        <v>6633611264</v>
+        <v>8234829099.417403</v>
       </c>
       <c r="K265" s="25" t="inlineStr">
         <is>
@@ -17941,21 +17941,21 @@
         </is>
       </c>
       <c r="L265" s="22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M265" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N265" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, LynchEV-GY, OakDeleveraging, Forensic-PayoutConfirmed, F</t>
+          <t>KPIThreshold, ONeil-CANSLIM, Kullamagi-Breakout, StrongCoverage, XR-GA</t>
         </is>
       </c>
       <c r="O265" s="24" t="n">
-        <v>0.4270649011740091</v>
+        <v>0.4594681108543432</v>
       </c>
       <c r="P265" s="24" t="n">
-        <v>0.182031712</v>
+        <v>0.2039989197</v>
       </c>
     </row>
     <row r="266" ht="16" customHeight="1">
@@ -17969,62 +17969,127 @@
       </c>
       <c r="D266" s="18" t="inlineStr">
         <is>
+          <t>PTGCF</t>
+        </is>
+      </c>
+      <c r="E266" s="19" t="inlineStr">
+        <is>
+          <t>PTT Global Chemical Public Company Limited</t>
+        </is>
+      </c>
+      <c r="F266" s="26" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G266" s="21" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="H266" s="21" t="inlineStr">
+        <is>
+          <t>Chemicals</t>
+        </is>
+      </c>
+      <c r="I266" s="16" t="inlineStr">
+        <is>
+          <t>Mid Cap</t>
+        </is>
+      </c>
+      <c r="J266" s="22" t="n">
+        <v>6633611264</v>
+      </c>
+      <c r="K266" s="25" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="L266" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="M266" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="N266" s="21" t="inlineStr">
+        <is>
+          <t>KPIThreshold, LynchEV-GY, OakDeleveraging, Forensic-PayoutConfirmed, F</t>
+        </is>
+      </c>
+      <c r="O266" s="24" t="n">
+        <v>0.4270649011740091</v>
+      </c>
+      <c r="P266" s="24" t="n">
+        <v>0.182031712</v>
+      </c>
+    </row>
+    <row r="267" ht="16" customHeight="1">
+      <c r="B267" s="16" t="n">
+        <v>264</v>
+      </c>
+      <c r="C267" s="17" t="inlineStr">
+        <is>
+          <t>STRICT</t>
+        </is>
+      </c>
+      <c r="D267" s="18" t="inlineStr">
+        <is>
           <t>TAWNF</t>
         </is>
       </c>
-      <c r="E266" s="19" t="inlineStr">
+      <c r="E267" s="19" t="inlineStr">
         <is>
           <t>Thai Airways International Public Company Limited</t>
         </is>
       </c>
-      <c r="F266" s="26" t="inlineStr">
+      <c r="F267" s="26" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G266" s="21" t="inlineStr">
+      <c r="G267" s="21" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="H266" s="21" t="inlineStr">
+      <c r="H267" s="21" t="inlineStr">
         <is>
           <t>Airlines</t>
         </is>
       </c>
-      <c r="I266" s="16" t="inlineStr">
-        <is>
-          <t>Mid Cap</t>
-        </is>
-      </c>
-      <c r="J266" s="22" t="n">
+      <c r="I267" s="16" t="inlineStr">
+        <is>
+          <t>Mid Cap</t>
+        </is>
+      </c>
+      <c r="J267" s="22" t="n">
         <v>4853073408</v>
       </c>
-      <c r="K266" s="25" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
-        </is>
-      </c>
-      <c r="L266" s="22" t="n">
+      <c r="K267" s="25" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
+        </is>
+      </c>
+      <c r="L267" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="M266" s="22" t="n">
+      <c r="M267" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="N266" s="21" t="inlineStr">
+      <c r="N267" s="21" t="inlineStr">
         <is>
           <t>KPIThreshold, StrongCoverage, LynchEV-GY, Forensic-PayoutConfirmed, Fo</t>
         </is>
       </c>
-      <c r="O266" s="24" t="n">
+      <c r="O267" s="24" t="n">
         <v>0.4280730538412396</v>
       </c>
-      <c r="P266" s="24" t="n">
+      <c r="P267" s="24" t="n">
         <v>0.1695166</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B3:P266"/>
+  <autoFilter ref="B3:P267"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
@@ -18039,7 +18104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P269"/>
+  <dimension ref="A1:P268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -18064,7 +18129,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STRONG — watchlist — 266 names</t>
+          <t xml:space="preserve">  STRONG — watchlist — 265 names</t>
         </is>
       </c>
       <c r="B1" s="11" t="n"/>
@@ -24758,58 +24823,58 @@
       </c>
       <c r="D106" s="18" t="inlineStr">
         <is>
-          <t>PIFMY</t>
+          <t>VNA.DE</t>
         </is>
       </c>
       <c r="E106" s="19" t="inlineStr">
         <is>
-          <t>PT Indofood Sukses Makmur Tbk</t>
+          <t>Vonovia SE</t>
         </is>
       </c>
       <c r="F106" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G106" s="21" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="H106" s="21" t="inlineStr">
         <is>
-          <t>Food &amp; Staples Retailing</t>
+          <t>Real Estate Management &amp; Development</t>
         </is>
       </c>
       <c r="I106" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="J106" s="22" t="n">
-        <v>3487585536</v>
-      </c>
-      <c r="K106" s="25" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>17725510292.5708</v>
+      </c>
+      <c r="K106" s="26" t="inlineStr">
+        <is>
+          <t>YELLOW</t>
         </is>
       </c>
       <c r="L106" s="22" t="n">
+        <v>3</v>
+      </c>
+      <c r="M106" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="M106" s="22" t="n">
-        <v>3</v>
-      </c>
       <c r="N106" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, MidCapGARP, LynchEV-GY, LigerLaggingInflect, NegativeEV-</t>
+          <t>LynchPEGY, AsleepAtWheel-Beats, AsleepUnrerated-BeatsNoRerate, Analyst</t>
         </is>
       </c>
       <c r="O106" s="24" t="n">
-        <v>0.3979056090610184</v>
+        <v>0.4370623405061705</v>
       </c>
       <c r="P106" s="24" t="n">
-        <v>0.409080105</v>
+        <v>0.4090182828</v>
       </c>
     </row>
     <row r="107" ht="16" customHeight="1">
@@ -24823,27 +24888,27 @@
       </c>
       <c r="D107" s="18" t="inlineStr">
         <is>
-          <t>VNA.DE</t>
+          <t>NJDCY</t>
         </is>
       </c>
       <c r="E107" s="19" t="inlineStr">
         <is>
-          <t>Vonovia SE</t>
+          <t>Nidec Corp.</t>
         </is>
       </c>
       <c r="F107" s="26" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G107" s="21" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H107" s="21" t="inlineStr">
         <is>
-          <t>Real Estate Management &amp; Development</t>
+          <t>Machinery</t>
         </is>
       </c>
       <c r="I107" s="16" t="inlineStr">
@@ -24852,29 +24917,29 @@
         </is>
       </c>
       <c r="J107" s="22" t="n">
-        <v>17725510292.5708</v>
-      </c>
-      <c r="K107" s="26" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+        <v>17872109568</v>
+      </c>
+      <c r="K107" s="25" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="L107" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="M107" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="M107" s="22" t="n">
-        <v>5</v>
-      </c>
       <c r="N107" s="21" t="inlineStr">
         <is>
-          <t>LynchPEGY, AsleepAtWheel-Beats, AsleepUnrerated-BeatsNoRerate, Analyst</t>
+          <t>NarrativeLag, FixedCost+DemandShock, BAB-Becoming, LynchPEGY, XR-Foren</t>
         </is>
       </c>
       <c r="O107" s="24" t="n">
-        <v>0.4370623405061705</v>
+        <v>0.3921379635500283</v>
       </c>
       <c r="P107" s="24" t="n">
-        <v>0.4090182828</v>
+        <v>0.4088271616</v>
       </c>
     </row>
     <row r="108" ht="16" customHeight="1">
@@ -24888,27 +24953,27 @@
       </c>
       <c r="D108" s="18" t="inlineStr">
         <is>
-          <t>NJDCY</t>
+          <t>S19.F</t>
         </is>
       </c>
       <c r="E108" s="19" t="inlineStr">
         <is>
-          <t>Nidec Corp.</t>
+          <t>Sumitomo Metal Mining Co., Ltd.</t>
         </is>
       </c>
       <c r="F108" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G108" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H108" s="21" t="inlineStr">
         <is>
-          <t>Machinery</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="I108" s="16" t="inlineStr">
@@ -24917,7 +24982,7 @@
         </is>
       </c>
       <c r="J108" s="22" t="n">
-        <v>17872109568</v>
+        <v>15955593706.04883</v>
       </c>
       <c r="K108" s="25" t="inlineStr">
         <is>
@@ -24925,21 +24990,21 @@
         </is>
       </c>
       <c r="L108" s="22" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M108" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N108" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, BAB-Becoming, LynchPEGY, XR-Foren</t>
+          <t>NarrativeLag, RegimeCyclical, KPIThreshold, MidCapGARP, LynchPEGY, Lyn</t>
         </is>
       </c>
       <c r="O108" s="24" t="n">
-        <v>0.3921379635500283</v>
+        <v>0.3945448253103275</v>
       </c>
       <c r="P108" s="24" t="n">
-        <v>0.4088271616</v>
+        <v>0.40870859</v>
       </c>
     </row>
     <row r="109" ht="16" customHeight="1">
@@ -24953,36 +25018,36 @@
       </c>
       <c r="D109" s="18" t="inlineStr">
         <is>
-          <t>S19.F</t>
+          <t>FPAFY</t>
         </is>
       </c>
       <c r="E109" s="19" t="inlineStr">
         <is>
-          <t>Sumitomo Metal Mining Co., Ltd.</t>
+          <t>First Pacific Company Ltd.</t>
         </is>
       </c>
       <c r="F109" s="26" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G109" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="H109" s="21" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Food &amp; Staples Retailing</t>
         </is>
       </c>
       <c r="I109" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="J109" s="22" t="n">
-        <v>15955593706.04883</v>
+        <v>2761853696</v>
       </c>
       <c r="K109" s="25" t="inlineStr">
         <is>
@@ -24990,21 +25055,21 @@
         </is>
       </c>
       <c r="L109" s="22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M109" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N109" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, RegimeCyclical, KPIThreshold, MidCapGARP, LynchPEGY, Lyn</t>
+          <t>NarrativeLag, MidCapGARP, CapitalReturner, BAB-Becoming, LynchEV-GY, F</t>
         </is>
       </c>
       <c r="O109" s="24" t="n">
-        <v>0.3945448253103275</v>
+        <v>0.3783389786892444</v>
       </c>
       <c r="P109" s="24" t="n">
-        <v>0.40870859</v>
+        <v>0.408606</v>
       </c>
     </row>
     <row r="110" ht="16" customHeight="1">
@@ -25018,12 +25083,12 @@
       </c>
       <c r="D110" s="18" t="inlineStr">
         <is>
-          <t>FPAFY</t>
+          <t>NNDNF</t>
         </is>
       </c>
       <c r="E110" s="19" t="inlineStr">
         <is>
-          <t>First Pacific Company Ltd.</t>
+          <t>Nidec Corp.</t>
         </is>
       </c>
       <c r="F110" s="26" t="inlineStr">
@@ -25033,21 +25098,21 @@
       </c>
       <c r="G110" s="21" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H110" s="21" t="inlineStr">
         <is>
-          <t>Food &amp; Staples Retailing</t>
+          <t>Machinery</t>
         </is>
       </c>
       <c r="I110" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="J110" s="22" t="n">
-        <v>2761853696</v>
+        <v>19198672896</v>
       </c>
       <c r="K110" s="25" t="inlineStr">
         <is>
@@ -25055,21 +25120,21 @@
         </is>
       </c>
       <c r="L110" s="22" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M110" s="22" t="n">
         <v>3</v>
       </c>
       <c r="N110" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, MidCapGARP, CapitalReturner, BAB-Becoming, LynchEV-GY, F</t>
+          <t>NarrativeLag, FixedCost+DemandShock, RegimeCyclical, BAB-Becoming, Lyn</t>
         </is>
       </c>
       <c r="O110" s="24" t="n">
-        <v>0.3783389786892444</v>
+        <v>0.391851000844459</v>
       </c>
       <c r="P110" s="24" t="n">
-        <v>0.408606</v>
+        <v>0.4085282943999999</v>
       </c>
     </row>
     <row r="111" ht="16" customHeight="1">
@@ -25083,27 +25148,27 @@
       </c>
       <c r="D111" s="18" t="inlineStr">
         <is>
-          <t>NNDNF</t>
+          <t>EQX.TO</t>
         </is>
       </c>
       <c r="E111" s="19" t="inlineStr">
         <is>
-          <t>Nidec Corp.</t>
+          <t>Equinox Gold Corp.</t>
         </is>
       </c>
       <c r="F111" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G111" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H111" s="21" t="inlineStr">
         <is>
-          <t>Machinery</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="I111" s="16" t="inlineStr">
@@ -25112,7 +25177,7 @@
         </is>
       </c>
       <c r="J111" s="22" t="n">
-        <v>19198672896</v>
+        <v>14354527646.84619</v>
       </c>
       <c r="K111" s="25" t="inlineStr">
         <is>
@@ -25120,21 +25185,21 @@
         </is>
       </c>
       <c r="L111" s="22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M111" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N111" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, RegimeCyclical, BAB-Becoming, Lyn</t>
+          <t>FixedCost+DemandShock, RegimeCyclical, KPIThreshold, LynchPEGY, LynchE</t>
         </is>
       </c>
       <c r="O111" s="24" t="n">
-        <v>0.391851000844459</v>
+        <v>0.3891677996930489</v>
       </c>
       <c r="P111" s="24" t="n">
-        <v>0.4085282943999999</v>
+        <v>0.4082525656</v>
       </c>
     </row>
     <row r="112" ht="16" customHeight="1">
@@ -25148,36 +25213,36 @@
       </c>
       <c r="D112" s="18" t="inlineStr">
         <is>
-          <t>EQX.TO</t>
+          <t>PIFMY</t>
         </is>
       </c>
       <c r="E112" s="19" t="inlineStr">
         <is>
-          <t>Equinox Gold Corp.</t>
+          <t>PT Indofood Sukses Makmur Tbk</t>
         </is>
       </c>
       <c r="F112" s="26" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G112" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="H112" s="21" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Food &amp; Staples Retailing</t>
         </is>
       </c>
       <c r="I112" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="J112" s="22" t="n">
-        <v>14354527646.84619</v>
+        <v>3487585536</v>
       </c>
       <c r="K112" s="25" t="inlineStr">
         <is>
@@ -25185,21 +25250,21 @@
         </is>
       </c>
       <c r="L112" s="22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M112" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N112" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, RegimeCyclical, KPIThreshold, LynchPEGY, LynchE</t>
+          <t>NarrativeLag, MidCapGARP, LynchEV-GY, LigerLaggingInflect</t>
         </is>
       </c>
       <c r="O112" s="24" t="n">
-        <v>0.3891677996930489</v>
+        <v>0.3979056090610184</v>
       </c>
       <c r="P112" s="24" t="n">
-        <v>0.4082525656</v>
+        <v>0.4078546668</v>
       </c>
     </row>
     <row r="113" ht="16" customHeight="1">
@@ -34793,27 +34858,27 @@
       </c>
       <c r="D261" s="18" t="inlineStr">
         <is>
-          <t>TSUSF</t>
+          <t>CUPID.NS</t>
         </is>
       </c>
       <c r="E261" s="19" t="inlineStr">
         <is>
-          <t>Tsuruha Holdings Inc.</t>
+          <t>Cupid Limited</t>
         </is>
       </c>
       <c r="F261" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G261" s="21" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="H261" s="21" t="inlineStr">
         <is>
-          <t>Pharmaceuticals</t>
+          <t>Household Products</t>
         </is>
       </c>
       <c r="I261" s="16" t="inlineStr">
@@ -34822,7 +34887,7 @@
         </is>
       </c>
       <c r="J261" s="22" t="n">
-        <v>7815836672</v>
+        <v>3934702780.033697</v>
       </c>
       <c r="K261" s="25" t="inlineStr">
         <is>
@@ -34830,21 +34895,21 @@
         </is>
       </c>
       <c r="L261" s="22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M261" s="22" t="n">
         <v>3</v>
       </c>
       <c r="N261" s="21" t="inlineStr">
         <is>
-          <t>LynchEV-GY, XR-PeerMarginGap, ExceptionalEVSG, TenBaggerPath</t>
+          <t>KPIThreshold, ONeil-CANSLIM, Weinstein-Stage2, Kullamagi-Breakout, Str</t>
         </is>
       </c>
       <c r="O261" s="24" t="n">
-        <v>0.5803731904418854</v>
+        <v>0.4632894424453107</v>
       </c>
       <c r="P261" s="24" t="n">
-        <v>0.239856232</v>
+        <v>0.2072124416</v>
       </c>
     </row>
     <row r="262" ht="16" customHeight="1">
@@ -34858,27 +34923,27 @@
       </c>
       <c r="D262" s="18" t="inlineStr">
         <is>
-          <t>CUPID.NS</t>
+          <t>3163.TWO</t>
         </is>
       </c>
       <c r="E262" s="19" t="inlineStr">
         <is>
-          <t>Cupid Limited</t>
+          <t>Browave Corporation</t>
         </is>
       </c>
       <c r="F262" s="26" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G262" s="21" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H262" s="21" t="inlineStr">
         <is>
-          <t>Household Products</t>
+          <t>Electrical Equipment</t>
         </is>
       </c>
       <c r="I262" s="16" t="inlineStr">
@@ -34887,7 +34952,7 @@
         </is>
       </c>
       <c r="J262" s="22" t="n">
-        <v>3934702780.033697</v>
+        <v>2008415999.30862</v>
       </c>
       <c r="K262" s="25" t="inlineStr">
         <is>
@@ -34895,21 +34960,21 @@
         </is>
       </c>
       <c r="L262" s="22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M262" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N262" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, ONeil-CANSLIM, Weinstein-Stage2, Kullamagi-Breakout, Str</t>
+          <t>FixedCost+DemandShock, KPIThreshold, StrongCoverage</t>
         </is>
       </c>
       <c r="O262" s="24" t="n">
-        <v>0.4632894424453107</v>
+        <v>0.3845576399215896</v>
       </c>
       <c r="P262" s="24" t="n">
-        <v>0.2072124416</v>
+        <v>0.1964484096</v>
       </c>
     </row>
     <row r="263" ht="16" customHeight="1">
@@ -34923,12 +34988,12 @@
       </c>
       <c r="D263" s="18" t="inlineStr">
         <is>
-          <t>3163.TWO</t>
+          <t>3443.TW</t>
         </is>
       </c>
       <c r="E263" s="19" t="inlineStr">
         <is>
-          <t>Browave Corporation</t>
+          <t>Global Unichip Corp.</t>
         </is>
       </c>
       <c r="F263" s="26" t="inlineStr">
@@ -34938,21 +35003,21 @@
       </c>
       <c r="G263" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H263" s="21" t="inlineStr">
         <is>
-          <t>Electrical Equipment</t>
+          <t>Semiconductors &amp; Semiconductor Equipment</t>
         </is>
       </c>
       <c r="I263" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="J263" s="22" t="n">
-        <v>2008415999.30862</v>
+        <v>25978691751.36103</v>
       </c>
       <c r="K263" s="25" t="inlineStr">
         <is>
@@ -34960,21 +35025,21 @@
         </is>
       </c>
       <c r="L263" s="22" t="n">
+        <v>4</v>
+      </c>
+      <c r="M263" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="M263" s="22" t="n">
-        <v>4</v>
-      </c>
       <c r="N263" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, KPIThreshold, StrongCoverage</t>
+          <t>KPIThreshold, Kullamagi-Breakout, StrongCoverage, AsleepAtWheel-Beats</t>
         </is>
       </c>
       <c r="O263" s="24" t="n">
-        <v>0.3845576399215896</v>
+        <v>0.411066815259984</v>
       </c>
       <c r="P263" s="24" t="n">
-        <v>0.1964484096</v>
+        <v>0.1930396356</v>
       </c>
     </row>
     <row r="264" ht="16" customHeight="1">
@@ -34988,17 +35053,17 @@
       </c>
       <c r="D264" s="18" t="inlineStr">
         <is>
-          <t>3443.TW</t>
+          <t>ATS.VI</t>
         </is>
       </c>
       <c r="E264" s="19" t="inlineStr">
         <is>
-          <t>Global Unichip Corp.</t>
+          <t>AT &amp; S Austria Technologie &amp; Systemtechnik Aktiengesellschaf</t>
         </is>
       </c>
       <c r="F264" s="26" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="G264" s="21" t="inlineStr">
@@ -35008,16 +35073,16 @@
       </c>
       <c r="H264" s="21" t="inlineStr">
         <is>
-          <t>Semiconductors &amp; Semiconductor Equipment</t>
+          <t>Electronic Equipment, Instruments &amp; Components</t>
         </is>
       </c>
       <c r="I264" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="J264" s="22" t="n">
-        <v>25978691751.36103</v>
+        <v>7459774071.350098</v>
       </c>
       <c r="K264" s="25" t="inlineStr">
         <is>
@@ -35032,14 +35097,14 @@
       </c>
       <c r="N264" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, Kullamagi-Breakout, StrongCoverage, AsleepAtWheel-Beats</t>
+          <t>KPIThreshold, LynchEV-GY, XR-GAAPProfitCrossover, AsleepAtWheel-Beats</t>
         </is>
       </c>
       <c r="O264" s="24" t="n">
-        <v>0.411066815259984</v>
+        <v>0.4084457065283332</v>
       </c>
       <c r="P264" s="24" t="n">
-        <v>0.1930396356</v>
+        <v>0.179579952</v>
       </c>
     </row>
     <row r="265" ht="16" customHeight="1">
@@ -35053,17 +35118,17 @@
       </c>
       <c r="D265" s="18" t="inlineStr">
         <is>
-          <t>ATS.VI</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="E265" s="19" t="inlineStr">
         <is>
-          <t>AT &amp; S Austria Technologie &amp; Systemtechnik Aktiengesellschaf</t>
+          <t>Lumentum Holdings Inc.</t>
         </is>
       </c>
       <c r="F265" s="26" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G265" s="21" t="inlineStr">
@@ -35073,16 +35138,16 @@
       </c>
       <c r="H265" s="21" t="inlineStr">
         <is>
-          <t>Electronic Equipment, Instruments &amp; Components</t>
+          <t>Communications Equipment</t>
         </is>
       </c>
       <c r="I265" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="J265" s="22" t="n">
-        <v>7459774071.350098</v>
+        <v>83154591744</v>
       </c>
       <c r="K265" s="25" t="inlineStr">
         <is>
@@ -35090,21 +35155,21 @@
         </is>
       </c>
       <c r="L265" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="M265" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="M265" s="22" t="n">
-        <v>3</v>
-      </c>
       <c r="N265" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, LynchEV-GY, XR-GAAPProfitCrossover, AsleepAtWheel-Beats</t>
+          <t>KPIThreshold, Kullamagi-Breakout, StrongCoverage, GeographicGlobal, Fa</t>
         </is>
       </c>
       <c r="O265" s="24" t="n">
-        <v>0.4084457065283332</v>
+        <v>0.4060982629302042</v>
       </c>
       <c r="P265" s="24" t="n">
-        <v>0.179579952</v>
+        <v>0.17280249</v>
       </c>
     </row>
     <row r="266" ht="16" customHeight="1">
@@ -35118,17 +35183,17 @@
       </c>
       <c r="D266" s="18" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>603629.SS</t>
         </is>
       </c>
       <c r="E266" s="19" t="inlineStr">
         <is>
-          <t>Lumentum Holdings Inc.</t>
+          <t>Jiangsu Lettall Electronic Co.,Ltd</t>
         </is>
       </c>
       <c r="F266" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G266" s="21" t="inlineStr">
@@ -35138,16 +35203,16 @@
       </c>
       <c r="H266" s="21" t="inlineStr">
         <is>
-          <t>Communications Equipment</t>
+          <t>Electronic Equipment, Instruments &amp; Components</t>
         </is>
       </c>
       <c r="I266" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="J266" s="22" t="n">
-        <v>83154591744</v>
+        <v>5706765811.490234</v>
       </c>
       <c r="K266" s="25" t="inlineStr">
         <is>
@@ -35155,21 +35220,21 @@
         </is>
       </c>
       <c r="L266" s="22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M266" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N266" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, Kullamagi-Breakout, StrongCoverage, GeographicGlobal, Fa</t>
+          <t>KPIThreshold, LynchPEGY, TenBaggerPath, Flyover-QuietQuality</t>
         </is>
       </c>
       <c r="O266" s="24" t="n">
-        <v>0.4060982629302042</v>
+        <v>0.3669523844596213</v>
       </c>
       <c r="P266" s="24" t="n">
-        <v>0.17280249</v>
+        <v>0.1585236</v>
       </c>
     </row>
     <row r="267" ht="16" customHeight="1">
@@ -35183,17 +35248,17 @@
       </c>
       <c r="D267" s="18" t="inlineStr">
         <is>
-          <t>603629.SS</t>
+          <t>STLTECH.NS</t>
         </is>
       </c>
       <c r="E267" s="19" t="inlineStr">
         <is>
-          <t>Jiangsu Lettall Electronic Co.,Ltd</t>
+          <t>Sterlite Technologies Limited</t>
         </is>
       </c>
       <c r="F267" s="26" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G267" s="21" t="inlineStr">
@@ -35203,7 +35268,7 @@
       </c>
       <c r="H267" s="21" t="inlineStr">
         <is>
-          <t>Electronic Equipment, Instruments &amp; Components</t>
+          <t>Communications Equipment</t>
         </is>
       </c>
       <c r="I267" s="16" t="inlineStr">
@@ -35212,7 +35277,7 @@
         </is>
       </c>
       <c r="J267" s="22" t="n">
-        <v>5706765811.490234</v>
+        <v>4819648350.224731</v>
       </c>
       <c r="K267" s="25" t="inlineStr">
         <is>
@@ -35227,14 +35292,14 @@
       </c>
       <c r="N267" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, LynchPEGY, TenBaggerPath, Flyover-QuietQuality</t>
+          <t>KPIThreshold, Weinstein-Stage2, Kullamagi-Breakout, XR-GAAPProfitCross</t>
         </is>
       </c>
       <c r="O267" s="24" t="n">
-        <v>0.3669523844596213</v>
+        <v>0.3580368541442796</v>
       </c>
       <c r="P267" s="24" t="n">
-        <v>0.1585236</v>
+        <v>0.1546716</v>
       </c>
     </row>
     <row r="268" ht="16" customHeight="1">
@@ -35248,36 +35313,36 @@
       </c>
       <c r="D268" s="18" t="inlineStr">
         <is>
-          <t>STLTECH.NS</t>
+          <t>TIAOF</t>
         </is>
       </c>
       <c r="E268" s="19" t="inlineStr">
         <is>
-          <t>Sterlite Technologies Limited</t>
+          <t>Telecom Italia S.p.A.</t>
         </is>
       </c>
       <c r="F268" s="26" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G268" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="H268" s="21" t="inlineStr">
         <is>
-          <t>Communications Equipment</t>
+          <t>Diversified Telecommunication Services</t>
         </is>
       </c>
       <c r="I268" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="J268" s="22" t="n">
-        <v>4819648350.224731</v>
+        <v>18559361024</v>
       </c>
       <c r="K268" s="25" t="inlineStr">
         <is>
@@ -35296,79 +35361,14 @@
         </is>
       </c>
       <c r="O268" s="24" t="n">
-        <v>0.3580368541442796</v>
+        <v>0.3606072781109206</v>
       </c>
       <c r="P268" s="24" t="n">
-        <v>0.1546716</v>
-      </c>
-    </row>
-    <row r="269" ht="16" customHeight="1">
-      <c r="B269" s="16" t="n">
-        <v>266</v>
-      </c>
-      <c r="C269" s="17" t="inlineStr">
-        <is>
-          <t>STRONG</t>
-        </is>
-      </c>
-      <c r="D269" s="18" t="inlineStr">
-        <is>
-          <t>TIAOF</t>
-        </is>
-      </c>
-      <c r="E269" s="19" t="inlineStr">
-        <is>
-          <t>Telecom Italia S.p.A.</t>
-        </is>
-      </c>
-      <c r="F269" s="26" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="G269" s="21" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="H269" s="21" t="inlineStr">
-        <is>
-          <t>Diversified Telecommunication Services</t>
-        </is>
-      </c>
-      <c r="I269" s="16" t="inlineStr">
-        <is>
-          <t>Large Cap</t>
-        </is>
-      </c>
-      <c r="J269" s="22" t="n">
-        <v>18559361024</v>
-      </c>
-      <c r="K269" s="25" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
-        </is>
-      </c>
-      <c r="L269" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="M269" s="22" t="n">
-        <v>3</v>
-      </c>
-      <c r="N269" s="21" t="inlineStr">
-        <is>
-          <t>KPIThreshold, Weinstein-Stage2, Kullamagi-Breakout, XR-GAAPProfitCross</t>
-        </is>
-      </c>
-      <c r="O269" s="24" t="n">
-        <v>0.3606072781109206</v>
-      </c>
-      <c r="P269" s="24" t="n">
         <v>0.1493827233</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B3:P269"/>
+  <autoFilter ref="B3:P268"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
@@ -35943,7 +35943,7 @@
         </is>
       </c>
       <c r="L10" s="22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M10" s="22" t="n">
         <v>2</v>
@@ -36264,14 +36264,14 @@
         </is>
       </c>
       <c r="L15" s="22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M15" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N15" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, CapitalReturner, NetCashReturner, StrongCoverage, LigerL</t>
+          <t>NarrativeLag, CapitalReturner, NetCashReturner, StrongCoverage, LynchE</t>
         </is>
       </c>
       <c r="O15" s="24" t="n">
@@ -40489,12 +40489,12 @@
       </c>
       <c r="D81" s="18" t="inlineStr">
         <is>
-          <t>AYYLF</t>
+          <t>CIHKY</t>
         </is>
       </c>
       <c r="E81" s="19" t="inlineStr">
         <is>
-          <t>Ayala Corporation</t>
+          <t>China Merchants Bank Co., Ltd.</t>
         </is>
       </c>
       <c r="F81" s="26" t="inlineStr">
@@ -40504,21 +40504,21 @@
       </c>
       <c r="G81" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="H81" s="21" t="inlineStr">
         <is>
-          <t>Industrial Conglomerates</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="I81" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="J81" s="22" t="n">
-        <v>5110343680</v>
+        <v>166955368448</v>
       </c>
       <c r="K81" s="25" t="inlineStr">
         <is>
@@ -40526,21 +40526,21 @@
         </is>
       </c>
       <c r="L81" s="22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M81" s="22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N81" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, MidCapGARP, NetCashReturner, LynchEV-GY, XR-CyclicalTrou</t>
+          <t>FinancialsValue, Weinstein-Stage2, LynchPEGY</t>
         </is>
       </c>
       <c r="O81" s="24" t="n">
-        <v>0.375730911793973</v>
+        <v>0.3789959204316813</v>
       </c>
       <c r="P81" s="24" t="n">
-        <v>0.5162614800000001</v>
+        <v>0.5152824</v>
       </c>
     </row>
     <row r="82" ht="16" customHeight="1">
@@ -40554,12 +40554,12 @@
       </c>
       <c r="D82" s="18" t="inlineStr">
         <is>
-          <t>CIHKY</t>
+          <t>KFY</t>
         </is>
       </c>
       <c r="E82" s="19" t="inlineStr">
         <is>
-          <t>China Merchants Bank Co., Ltd.</t>
+          <t>Korn Ferry</t>
         </is>
       </c>
       <c r="F82" s="26" t="inlineStr">
@@ -40569,21 +40569,21 @@
       </c>
       <c r="G82" s="21" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H82" s="21" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Professional Services</t>
         </is>
       </c>
       <c r="I82" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="J82" s="22" t="n">
-        <v>166955368448</v>
+        <v>4233221120</v>
       </c>
       <c r="K82" s="25" t="inlineStr">
         <is>
@@ -40591,21 +40591,21 @@
         </is>
       </c>
       <c r="L82" s="22" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="M82" s="22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N82" s="21" t="inlineStr">
         <is>
-          <t>FinancialsValue, Weinstein-Stage2, LynchPEGY</t>
+          <t>FixedCost+DemandShock, CapitalDiscipline, DurableReinvest, CheapPerROI</t>
         </is>
       </c>
       <c r="O82" s="24" t="n">
-        <v>0.3789959204316813</v>
+        <v>0.4791088848212037</v>
       </c>
       <c r="P82" s="24" t="n">
-        <v>0.5152824</v>
+        <v>0.5151522376000001</v>
       </c>
     </row>
     <row r="83" ht="16" customHeight="1">
@@ -40619,12 +40619,12 @@
       </c>
       <c r="D83" s="18" t="inlineStr">
         <is>
-          <t>KFY</t>
+          <t>GNW</t>
         </is>
       </c>
       <c r="E83" s="19" t="inlineStr">
         <is>
-          <t>Korn Ferry</t>
+          <t>Genworth Financial, Inc.</t>
         </is>
       </c>
       <c r="F83" s="26" t="inlineStr">
@@ -40634,12 +40634,12 @@
       </c>
       <c r="G83" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="H83" s="21" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="I83" s="16" t="inlineStr">
@@ -40648,7 +40648,7 @@
         </is>
       </c>
       <c r="J83" s="22" t="n">
-        <v>4233221120</v>
+        <v>3963657216</v>
       </c>
       <c r="K83" s="25" t="inlineStr">
         <is>
@@ -40656,21 +40656,21 @@
         </is>
       </c>
       <c r="L83" s="22" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="M83" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N83" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, CapitalDiscipline, DurableReinvest, CheapPerROI</t>
+          <t>Weinstein-Stage2, Forensic-PayoutConfirmed, Forensic-BookCompounder</t>
         </is>
       </c>
       <c r="O83" s="24" t="n">
-        <v>0.4791088848212037</v>
+        <v>0.3886650993162909</v>
       </c>
       <c r="P83" s="24" t="n">
-        <v>0.5151522376000001</v>
+        <v>0.5148748440000001</v>
       </c>
     </row>
     <row r="84" ht="16" customHeight="1">
@@ -40684,12 +40684,12 @@
       </c>
       <c r="D84" s="18" t="inlineStr">
         <is>
-          <t>GNW</t>
+          <t>CART</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr">
         <is>
-          <t>Genworth Financial, Inc.</t>
+          <t>Maplebear Inc.</t>
         </is>
       </c>
       <c r="F84" s="26" t="inlineStr">
@@ -40699,21 +40699,17 @@
       </c>
       <c r="G84" s="21" t="inlineStr">
         <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="H84" s="21" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="H84" s="21" t="n"/>
       <c r="I84" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="J84" s="22" t="n">
-        <v>3963657216</v>
+        <v>11280998400</v>
       </c>
       <c r="K84" s="25" t="inlineStr">
         <is>
@@ -40721,21 +40717,21 @@
         </is>
       </c>
       <c r="L84" s="22" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="M84" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N84" s="21" t="inlineStr">
         <is>
-          <t>Weinstein-Stage2, Forensic-PayoutConfirmed, Forensic-BookCompounder</t>
+          <t>CapitalDiscipline, LargeCapQuality, CapitalReturner, Weinstein-Stage2,</t>
         </is>
       </c>
       <c r="O84" s="24" t="n">
-        <v>0.3886650993162909</v>
+        <v>0.4606116694859642</v>
       </c>
       <c r="P84" s="24" t="n">
-        <v>0.5148748440000001</v>
+        <v>0.51417472</v>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1">
@@ -40749,12 +40745,12 @@
       </c>
       <c r="D85" s="18" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>SWRBF</t>
         </is>
       </c>
       <c r="E85" s="19" t="inlineStr">
         <is>
-          <t>Maplebear Inc.</t>
+          <t>Swire Pacific Limited</t>
         </is>
       </c>
       <c r="F85" s="26" t="inlineStr">
@@ -40764,17 +40760,21 @@
       </c>
       <c r="G85" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="H85" s="21" t="n"/>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="H85" s="21" t="inlineStr">
+        <is>
+          <t>Industrial Conglomerates</t>
+        </is>
+      </c>
       <c r="I85" s="16" t="inlineStr">
         <is>
           <t>Large Cap</t>
         </is>
       </c>
       <c r="J85" s="22" t="n">
-        <v>11280998400</v>
+        <v>10886654976</v>
       </c>
       <c r="K85" s="25" t="inlineStr">
         <is>
@@ -40782,21 +40782,21 @@
         </is>
       </c>
       <c r="L85" s="22" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="M85" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N85" s="21" t="inlineStr">
         <is>
-          <t>CapitalDiscipline, LargeCapQuality, CapitalReturner, Weinstein-Stage2,</t>
+          <t>FixedCost+DemandShock, CapitalReturner, Forensic-OverDepreciated, Fore</t>
         </is>
       </c>
       <c r="O85" s="24" t="n">
-        <v>0.4606116694859642</v>
+        <v>0.4823864540425946</v>
       </c>
       <c r="P85" s="24" t="n">
-        <v>0.51417472</v>
+        <v>0.5140304999999999</v>
       </c>
     </row>
     <row r="86" ht="16" customHeight="1">
@@ -40810,12 +40810,12 @@
       </c>
       <c r="D86" s="18" t="inlineStr">
         <is>
-          <t>SWRBF</t>
+          <t>HRSHF</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr">
         <is>
-          <t>Swire Pacific Limited</t>
+          <t>Haier Smart Home Co., Ltd. Class H</t>
         </is>
       </c>
       <c r="F86" s="26" t="inlineStr">
@@ -40825,12 +40825,12 @@
       </c>
       <c r="G86" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H86" s="21" t="inlineStr">
         <is>
-          <t>Industrial Conglomerates</t>
+          <t>Electronic Equipment, Instruments &amp; Components</t>
         </is>
       </c>
       <c r="I86" s="16" t="inlineStr">
@@ -40839,7 +40839,7 @@
         </is>
       </c>
       <c r="J86" s="22" t="n">
-        <v>10886654976</v>
+        <v>23722874880</v>
       </c>
       <c r="K86" s="25" t="inlineStr">
         <is>
@@ -40847,21 +40847,21 @@
         </is>
       </c>
       <c r="L86" s="22" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M86" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N86" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, CapitalReturner, Forensic-OverDepreciated, Fore</t>
+          <t>CapitalReturner, BalanceSheetReturn, StrongCoverage, LigerLaggingInfle</t>
         </is>
       </c>
       <c r="O86" s="24" t="n">
-        <v>0.4823864540425946</v>
+        <v>0.4487960654074911</v>
       </c>
       <c r="P86" s="24" t="n">
-        <v>0.5140304999999999</v>
+        <v>0.5137284</v>
       </c>
     </row>
     <row r="87" ht="16" customHeight="1">
@@ -40875,36 +40875,36 @@
       </c>
       <c r="D87" s="18" t="inlineStr">
         <is>
-          <t>HRSHF</t>
+          <t>600095.SS</t>
         </is>
       </c>
       <c r="E87" s="19" t="inlineStr">
         <is>
-          <t>Haier Smart Home Co., Ltd. Class H</t>
+          <t>Xiangcai Co., Ltd.</t>
         </is>
       </c>
       <c r="F87" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G87" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="H87" s="21" t="inlineStr">
         <is>
-          <t>Electronic Equipment, Instruments &amp; Components</t>
+          <t>Household Products</t>
         </is>
       </c>
       <c r="I87" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="J87" s="22" t="n">
-        <v>23722874880</v>
+        <v>3626018767.532593</v>
       </c>
       <c r="K87" s="25" t="inlineStr">
         <is>
@@ -40912,21 +40912,21 @@
         </is>
       </c>
       <c r="L87" s="22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M87" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N87" s="21" t="inlineStr">
         <is>
-          <t>CapitalReturner, BalanceSheetReturn, StrongCoverage, LigerLaggingInfle</t>
+          <t>NarrativeLag, BalanceSheetReturn, NetCashReturner, StrongCoverage, Lyn</t>
         </is>
       </c>
       <c r="O87" s="24" t="n">
-        <v>0.4487960654074911</v>
+        <v>0.4409834804508652</v>
       </c>
       <c r="P87" s="24" t="n">
-        <v>0.5137284</v>
+        <v>0.5122606664000001</v>
       </c>
     </row>
     <row r="88" ht="16" customHeight="1">
@@ -40940,27 +40940,27 @@
       </c>
       <c r="D88" s="18" t="inlineStr">
         <is>
-          <t>600095.SS</t>
+          <t>EVD.DE</t>
         </is>
       </c>
       <c r="E88" s="19" t="inlineStr">
         <is>
-          <t>Xiangcai Co., Ltd.</t>
+          <t>CTS Eventim AG &amp; Co. KGaA</t>
         </is>
       </c>
       <c r="F88" s="26" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G88" s="21" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="H88" s="21" t="inlineStr">
         <is>
-          <t>Household Products</t>
+          <t>Entertainment</t>
         </is>
       </c>
       <c r="I88" s="16" t="inlineStr">
@@ -40969,29 +40969,29 @@
         </is>
       </c>
       <c r="J88" s="22" t="n">
-        <v>3626018767.532593</v>
-      </c>
-      <c r="K88" s="25" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>6297144095.853516</v>
+      </c>
+      <c r="K88" s="23" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="L88" s="22" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="M88" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N88" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, BalanceSheetReturn, NetCashReturner, StrongCoverage, Lyn</t>
+          <t>NarrativeLag, DeadOption, MidCapGARP, StrongCoverage, BAB-Becoming, Ly</t>
         </is>
       </c>
       <c r="O88" s="24" t="n">
-        <v>0.4409834804508652</v>
+        <v>0.4524262018429997</v>
       </c>
       <c r="P88" s="24" t="n">
-        <v>0.5122606664000001</v>
+        <v>0.5121311468</v>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
@@ -41005,27 +41005,27 @@
       </c>
       <c r="D89" s="18" t="inlineStr">
         <is>
-          <t>EVD.DE</t>
+          <t>PAYC</t>
         </is>
       </c>
       <c r="E89" s="19" t="inlineStr">
         <is>
-          <t>CTS Eventim AG &amp; Co. KGaA</t>
+          <t>Paycom Software, Inc.</t>
         </is>
       </c>
       <c r="F89" s="26" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G89" s="21" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H89" s="21" t="inlineStr">
         <is>
-          <t>Entertainment</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="I89" s="16" t="inlineStr">
@@ -41034,29 +41034,29 @@
         </is>
       </c>
       <c r="J89" s="22" t="n">
-        <v>6297144095.853516</v>
-      </c>
-      <c r="K89" s="23" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+        <v>9866628096</v>
+      </c>
+      <c r="K89" s="25" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="L89" s="22" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="M89" s="22" t="n">
         <v>1</v>
       </c>
       <c r="N89" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, DeadOption, MidCapGARP, StrongCoverage, BAB-Becoming, Ly</t>
+          <t>NarrativeLag, CapitalDiscipline, LindyMargin, LindyFCF, QuietCompounde</t>
         </is>
       </c>
       <c r="O89" s="24" t="n">
-        <v>0.4524262018429997</v>
+        <v>0.4527245679569818</v>
       </c>
       <c r="P89" s="24" t="n">
-        <v>0.5121311468</v>
+        <v>0.5120041832000001</v>
       </c>
     </row>
     <row r="90" ht="16" customHeight="1">
@@ -41070,27 +41070,27 @@
       </c>
       <c r="D90" s="18" t="inlineStr">
         <is>
-          <t>PAYC</t>
+          <t>1651.HK</t>
         </is>
       </c>
       <c r="E90" s="19" t="inlineStr">
         <is>
-          <t>Paycom Software, Inc.</t>
+          <t>Precision Tsugami (China) Corporation Limited</t>
         </is>
       </c>
       <c r="F90" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G90" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H90" s="21" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Building Products</t>
         </is>
       </c>
       <c r="I90" s="16" t="inlineStr">
@@ -41099,7 +41099,7 @@
         </is>
       </c>
       <c r="J90" s="22" t="n">
-        <v>9866628096</v>
+        <v>2363603849.794249</v>
       </c>
       <c r="K90" s="25" t="inlineStr">
         <is>
@@ -41107,21 +41107,21 @@
         </is>
       </c>
       <c r="L90" s="22" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="M90" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N90" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, CapitalDiscipline, LindyMargin, LindyFCF, QuietCompounde</t>
+          <t>FixedCost+DemandShock, QuietCompounder, OwnerOperator, MidCapGARP, Str</t>
         </is>
       </c>
       <c r="O90" s="24" t="n">
-        <v>0.4527245679569818</v>
+        <v>0.4662269209277013</v>
       </c>
       <c r="P90" s="24" t="n">
-        <v>0.5120041832000001</v>
+        <v>0.5117830200000001</v>
       </c>
     </row>
     <row r="91" ht="16" customHeight="1">
@@ -41135,27 +41135,27 @@
       </c>
       <c r="D91" s="18" t="inlineStr">
         <is>
-          <t>1651.HK</t>
+          <t>900926.SS</t>
         </is>
       </c>
       <c r="E91" s="19" t="inlineStr">
         <is>
-          <t>Precision Tsugami (China) Corporation Limited</t>
+          <t>Shanghai Baosight Software Co.,Ltd.</t>
         </is>
       </c>
       <c r="F91" s="26" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G91" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H91" s="21" t="inlineStr">
         <is>
-          <t>Building Products</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="I91" s="16" t="inlineStr">
@@ -41164,7 +41164,7 @@
         </is>
       </c>
       <c r="J91" s="22" t="n">
-        <v>2363603849.794249</v>
+        <v>2412070912</v>
       </c>
       <c r="K91" s="25" t="inlineStr">
         <is>
@@ -41172,21 +41172,21 @@
         </is>
       </c>
       <c r="L91" s="22" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M91" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N91" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, QuietCompounder, OwnerOperator, MidCapGARP, Str</t>
+          <t>NarrativeLag, DeadOption, BalanceSheetReturn, StrongCoverage, LynchPEG</t>
         </is>
       </c>
       <c r="O91" s="24" t="n">
-        <v>0.4662269209277013</v>
+        <v>0.4680241826245717</v>
       </c>
       <c r="P91" s="24" t="n">
-        <v>0.5117830200000001</v>
+        <v>0.51147745</v>
       </c>
     </row>
     <row r="92" ht="16" customHeight="1">
@@ -41200,36 +41200,32 @@
       </c>
       <c r="D92" s="18" t="inlineStr">
         <is>
-          <t>900926.SS</t>
+          <t>MRP</t>
         </is>
       </c>
       <c r="E92" s="19" t="inlineStr">
         <is>
-          <t>Shanghai Baosight Software Co.,Ltd.</t>
+          <t>Millrose Properties, Inc.</t>
         </is>
       </c>
       <c r="F92" s="26" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G92" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="H92" s="21" t="inlineStr">
-        <is>
-          <t>Software</t>
-        </is>
-      </c>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="H92" s="21" t="n"/>
       <c r="I92" s="16" t="inlineStr">
         <is>
           <t>Mid Cap</t>
         </is>
       </c>
       <c r="J92" s="22" t="n">
-        <v>2412070912</v>
+        <v>4929963008</v>
       </c>
       <c r="K92" s="25" t="inlineStr">
         <is>
@@ -41237,21 +41233,21 @@
         </is>
       </c>
       <c r="L92" s="22" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M92" s="22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N92" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, DeadOption, BalanceSheetReturn, StrongCoverage, LynchPEG</t>
+          <t>LynchPEGY, InsiderConviction-SEC</t>
         </is>
       </c>
       <c r="O92" s="24" t="n">
-        <v>0.4680241826245717</v>
+        <v>0.4569553886753627</v>
       </c>
       <c r="P92" s="24" t="n">
-        <v>0.51147745</v>
+        <v>0.5107847999999999</v>
       </c>
     </row>
     <row r="93" ht="16" customHeight="1">
@@ -41265,32 +41261,36 @@
       </c>
       <c r="D93" s="18" t="inlineStr">
         <is>
-          <t>MRP</t>
+          <t>NWG.L</t>
         </is>
       </c>
       <c r="E93" s="19" t="inlineStr">
         <is>
-          <t>Millrose Properties, Inc.</t>
+          <t>NatWest Group plc</t>
         </is>
       </c>
       <c r="F93" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G93" s="21" t="inlineStr">
         <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="H93" s="21" t="n"/>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="H93" s="21" t="inlineStr">
+        <is>
+          <t>Banks</t>
+        </is>
+      </c>
       <c r="I93" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="J93" s="22" t="n">
-        <v>4929963008</v>
+        <v>73410600587.56494</v>
       </c>
       <c r="K93" s="25" t="inlineStr">
         <is>
@@ -41298,21 +41298,21 @@
         </is>
       </c>
       <c r="L93" s="22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M93" s="22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N93" s="21" t="inlineStr">
         <is>
-          <t>LynchPEGY, InsiderConviction-SEC</t>
+          <t>Weinstein-Stage2, LynchPEGY, AsleepAtWheel-Beats, AsleepUnrerated-Beat</t>
         </is>
       </c>
       <c r="O93" s="24" t="n">
-        <v>0.4569553886753627</v>
+        <v>0.3209231417148051</v>
       </c>
       <c r="P93" s="24" t="n">
-        <v>0.5107847999999999</v>
+        <v>0.51053298</v>
       </c>
     </row>
     <row r="94" ht="16" customHeight="1">
@@ -41326,36 +41326,36 @@
       </c>
       <c r="D94" s="18" t="inlineStr">
         <is>
-          <t>NWG.L</t>
+          <t>AYYLF</t>
         </is>
       </c>
       <c r="E94" s="19" t="inlineStr">
         <is>
-          <t>NatWest Group plc</t>
+          <t>Ayala Corporation</t>
         </is>
       </c>
       <c r="F94" s="26" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G94" s="21" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H94" s="21" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Industrial Conglomerates</t>
         </is>
       </c>
       <c r="I94" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="J94" s="22" t="n">
-        <v>73410600587.56494</v>
+        <v>5110343680</v>
       </c>
       <c r="K94" s="25" t="inlineStr">
         <is>
@@ -41363,21 +41363,21 @@
         </is>
       </c>
       <c r="L94" s="22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M94" s="22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N94" s="21" t="inlineStr">
         <is>
-          <t>Weinstein-Stage2, LynchPEGY, AsleepAtWheel-Beats, AsleepUnrerated-Beat</t>
+          <t>NarrativeLag, MidCapGARP, NetCashReturner, LynchEV-GY, XR-CyclicalTrou</t>
         </is>
       </c>
       <c r="O94" s="24" t="n">
-        <v>0.3209231417148051</v>
+        <v>0.375730911793973</v>
       </c>
       <c r="P94" s="24" t="n">
-        <v>0.51053298</v>
+        <v>0.510475791</v>
       </c>
     </row>
     <row r="95" ht="16" customHeight="1">
@@ -49793,27 +49793,27 @@
       </c>
       <c r="D225" s="18" t="inlineStr">
         <is>
-          <t>PHTCF</t>
+          <t>NAVINFLUOR.NS</t>
         </is>
       </c>
       <c r="E225" s="19" t="inlineStr">
         <is>
-          <t>PLDT Inc.</t>
+          <t>Navin Fluorine International Limited</t>
         </is>
       </c>
       <c r="F225" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="G225" s="21" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H225" s="21" t="inlineStr">
         <is>
-          <t>Diversified Telecommunication Services</t>
+          <t>Chemicals</t>
         </is>
       </c>
       <c r="I225" s="16" t="inlineStr">
@@ -49822,7 +49822,7 @@
         </is>
       </c>
       <c r="J225" s="22" t="n">
-        <v>4861255168</v>
+        <v>4581028753.371248</v>
       </c>
       <c r="K225" s="25" t="inlineStr">
         <is>
@@ -49830,21 +49830,21 @@
         </is>
       </c>
       <c r="L225" s="22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M225" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N225" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, CapitalReturner, NetCashReturner, LynchEV-GY, LigerLaggi</t>
+          <t>FixedCost+DemandShock, ONeil-CANSLIM, Weinstein-Stage2, StrongCoverage</t>
         </is>
       </c>
       <c r="O225" s="24" t="n">
-        <v>0.3425930168343006</v>
+        <v>0.4640265859605835</v>
       </c>
       <c r="P225" s="24" t="n">
-        <v>0.4572524250000001</v>
+        <v>0.45710304</v>
       </c>
     </row>
     <row r="226" ht="16" customHeight="1">
@@ -49858,27 +49858,27 @@
       </c>
       <c r="D226" s="18" t="inlineStr">
         <is>
-          <t>NAVINFLUOR.NS</t>
+          <t>3698.HK</t>
         </is>
       </c>
       <c r="E226" s="19" t="inlineStr">
         <is>
-          <t>Navin Fluorine International Limited</t>
+          <t>Huishang Bank Corporation Limited</t>
         </is>
       </c>
       <c r="F226" s="26" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G226" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="H226" s="21" t="inlineStr">
         <is>
-          <t>Chemicals</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="I226" s="16" t="inlineStr">
@@ -49887,7 +49887,7 @@
         </is>
       </c>
       <c r="J226" s="22" t="n">
-        <v>4581028753.371248</v>
+        <v>8613885759.288021</v>
       </c>
       <c r="K226" s="25" t="inlineStr">
         <is>
@@ -49895,21 +49895,21 @@
         </is>
       </c>
       <c r="L226" s="22" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M226" s="22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N226" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, ONeil-CANSLIM, Weinstein-Stage2, StrongCoverage</t>
+          <t>Weinstein-Stage2, LynchPEGY</t>
         </is>
       </c>
       <c r="O226" s="24" t="n">
-        <v>0.4640265859605835</v>
+        <v>0.4471291465149196</v>
       </c>
       <c r="P226" s="24" t="n">
-        <v>0.45710304</v>
+        <v>0.45709545</v>
       </c>
     </row>
     <row r="227" ht="16" customHeight="1">
@@ -49923,36 +49923,36 @@
       </c>
       <c r="D227" s="18" t="inlineStr">
         <is>
-          <t>3698.HK</t>
+          <t>KONMY</t>
         </is>
       </c>
       <c r="E227" s="19" t="inlineStr">
         <is>
-          <t>Huishang Bank Corporation Limited</t>
+          <t>Konami Holdings Corporation</t>
         </is>
       </c>
       <c r="F227" s="26" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G227" s="21" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="H227" s="21" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Interactive Media &amp; Services</t>
         </is>
       </c>
       <c r="I227" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="J227" s="22" t="n">
-        <v>8613885759.288021</v>
+        <v>17790433280</v>
       </c>
       <c r="K227" s="25" t="inlineStr">
         <is>
@@ -49960,21 +49960,21 @@
         </is>
       </c>
       <c r="L227" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="M227" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="M227" s="22" t="n">
-        <v>4</v>
-      </c>
       <c r="N227" s="21" t="inlineStr">
         <is>
-          <t>Weinstein-Stage2, LynchPEGY</t>
+          <t xml:space="preserve">NarrativeLag, LargeCapQuality, StrongCoverage, LynchPEGY, LynchEV-GY, </t>
         </is>
       </c>
       <c r="O227" s="24" t="n">
-        <v>0.4471291465149196</v>
+        <v>0.4323731223551612</v>
       </c>
       <c r="P227" s="24" t="n">
-        <v>0.45709545</v>
+        <v>0.4570013183999999</v>
       </c>
     </row>
     <row r="228" ht="16" customHeight="1">
@@ -49988,12 +49988,12 @@
       </c>
       <c r="D228" s="18" t="inlineStr">
         <is>
-          <t>KONMY</t>
+          <t>DBD</t>
         </is>
       </c>
       <c r="E228" s="19" t="inlineStr">
         <is>
-          <t>Konami Holdings Corporation</t>
+          <t>Diebold Nixdorf, Incorporated</t>
         </is>
       </c>
       <c r="F228" s="26" t="inlineStr">
@@ -50003,21 +50003,21 @@
       </c>
       <c r="G228" s="21" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H228" s="21" t="inlineStr">
         <is>
-          <t>Interactive Media &amp; Services</t>
+          <t>Software</t>
         </is>
       </c>
       <c r="I228" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="J228" s="22" t="n">
-        <v>17790433280</v>
+        <v>2227575296</v>
       </c>
       <c r="K228" s="25" t="inlineStr">
         <is>
@@ -50025,21 +50025,21 @@
         </is>
       </c>
       <c r="L228" s="22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M228" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N228" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">NarrativeLag, LargeCapQuality, StrongCoverage, LynchPEGY, LynchEV-GY, </t>
+          <t>CapitalDiscipline, KPIThreshold, CapitalReturner, LowSBCQuality, Geogr</t>
         </is>
       </c>
       <c r="O228" s="24" t="n">
-        <v>0.4323731223551612</v>
+        <v>0.3903658198976695</v>
       </c>
       <c r="P228" s="24" t="n">
-        <v>0.4570013183999999</v>
+        <v>0.4567277</v>
       </c>
     </row>
     <row r="229" ht="16" customHeight="1">
@@ -50053,12 +50053,12 @@
       </c>
       <c r="D229" s="18" t="inlineStr">
         <is>
-          <t>DBD</t>
+          <t>DDS</t>
         </is>
       </c>
       <c r="E229" s="19" t="inlineStr">
         <is>
-          <t>Diebold Nixdorf, Incorporated</t>
+          <t>Dillard’S, Inc.</t>
         </is>
       </c>
       <c r="F229" s="26" t="inlineStr">
@@ -50068,21 +50068,21 @@
       </c>
       <c r="G229" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="H229" s="21" t="inlineStr">
         <is>
-          <t>Software</t>
+          <t>Household Durables</t>
         </is>
       </c>
       <c r="I229" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="J229" s="22" t="n">
-        <v>2227575296</v>
+        <v>10161546240</v>
       </c>
       <c r="K229" s="25" t="inlineStr">
         <is>
@@ -50090,21 +50090,21 @@
         </is>
       </c>
       <c r="L229" s="22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M229" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N229" s="21" t="inlineStr">
         <is>
-          <t>CapitalDiscipline, KPIThreshold, CapitalReturner, LowSBCQuality, Geogr</t>
+          <t>FixedCost+DemandShock, QuietCompounder, OwnerOperator, CapitalReturner</t>
         </is>
       </c>
       <c r="O229" s="24" t="n">
-        <v>0.3903658198976695</v>
+        <v>0.39016453913511</v>
       </c>
       <c r="P229" s="24" t="n">
-        <v>0.4567277</v>
+        <v>0.4564924</v>
       </c>
     </row>
     <row r="230" ht="16" customHeight="1">
@@ -50118,36 +50118,32 @@
       </c>
       <c r="D230" s="18" t="inlineStr">
         <is>
-          <t>DDS</t>
+          <t>RITPF</t>
         </is>
       </c>
       <c r="E230" s="19" t="inlineStr">
         <is>
-          <t>Dillard’S, Inc.</t>
+          <t>RIT Capital Partners plc</t>
         </is>
       </c>
       <c r="F230" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G230" s="21" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="H230" s="21" t="inlineStr">
-        <is>
-          <t>Household Durables</t>
-        </is>
-      </c>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="H230" s="21" t="n"/>
       <c r="I230" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="J230" s="22" t="n">
-        <v>10161546240</v>
+        <v>4206580480</v>
       </c>
       <c r="K230" s="25" t="inlineStr">
         <is>
@@ -50155,21 +50151,21 @@
         </is>
       </c>
       <c r="L230" s="22" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="M230" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N230" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, QuietCompounder, OwnerOperator, CapitalReturner</t>
+          <t>FinancialsValue, Weinstein-Stage2, LynchPEGY</t>
         </is>
       </c>
       <c r="O230" s="24" t="n">
-        <v>0.39016453913511</v>
+        <v>0.4174950525510613</v>
       </c>
       <c r="P230" s="24" t="n">
-        <v>0.4564924</v>
+        <v>0.4562307932000001</v>
       </c>
     </row>
     <row r="231" ht="16" customHeight="1">
@@ -50183,32 +50179,36 @@
       </c>
       <c r="D231" s="18" t="inlineStr">
         <is>
-          <t>RITPF</t>
+          <t>SMTOY</t>
         </is>
       </c>
       <c r="E231" s="19" t="inlineStr">
         <is>
-          <t>RIT Capital Partners plc</t>
+          <t>Sumitomo Electric Industries, Ltd.</t>
         </is>
       </c>
       <c r="F231" s="26" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G231" s="21" t="inlineStr">
         <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="H231" s="21" t="n"/>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="H231" s="21" t="inlineStr">
+        <is>
+          <t>Auto Components</t>
+        </is>
+      </c>
       <c r="I231" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="J231" s="22" t="n">
-        <v>4206580480</v>
+        <v>42989182976</v>
       </c>
       <c r="K231" s="25" t="inlineStr">
         <is>
@@ -50216,21 +50216,21 @@
         </is>
       </c>
       <c r="L231" s="22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M231" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N231" s="21" t="inlineStr">
         <is>
-          <t>FinancialsValue, Weinstein-Stage2, LynchPEGY</t>
+          <t>FixedCost+DemandShock, MidCapGARP, LynchPEGY, LynchEV-GY</t>
         </is>
       </c>
       <c r="O231" s="24" t="n">
-        <v>0.4174950525510613</v>
+        <v>0.4748037517212048</v>
       </c>
       <c r="P231" s="24" t="n">
-        <v>0.4562307932000001</v>
+        <v>0.4560394</v>
       </c>
     </row>
     <row r="232" ht="16" customHeight="1">
@@ -50244,12 +50244,12 @@
       </c>
       <c r="D232" s="18" t="inlineStr">
         <is>
-          <t>SMTOY</t>
+          <t>AGX</t>
         </is>
       </c>
       <c r="E232" s="19" t="inlineStr">
         <is>
-          <t>Sumitomo Electric Industries, Ltd.</t>
+          <t>Argan Inc</t>
         </is>
       </c>
       <c r="F232" s="26" t="inlineStr">
@@ -50259,21 +50259,21 @@
       </c>
       <c r="G232" s="21" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H232" s="21" t="inlineStr">
         <is>
-          <t>Auto Components</t>
+          <t>Construction &amp; Engineering</t>
         </is>
       </c>
       <c r="I232" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="J232" s="22" t="n">
-        <v>42989182976</v>
+        <v>5804706816</v>
       </c>
       <c r="K232" s="25" t="inlineStr">
         <is>
@@ -50281,21 +50281,21 @@
         </is>
       </c>
       <c r="L232" s="22" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="M232" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N232" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, MidCapGARP, LynchPEGY, LynchEV-GY</t>
+          <t>DeadOption, CashReinvest, LindyFCF, NoDilution, LindyGrowth, BuybackCo</t>
         </is>
       </c>
       <c r="O232" s="24" t="n">
-        <v>0.4748037517212048</v>
+        <v>0.4169910857151652</v>
       </c>
       <c r="P232" s="24" t="n">
-        <v>0.4560394</v>
+        <v>0.45592386</v>
       </c>
     </row>
     <row r="233" ht="16" customHeight="1">
@@ -50309,12 +50309,12 @@
       </c>
       <c r="D233" s="18" t="inlineStr">
         <is>
-          <t>AGX</t>
+          <t>PHTCF</t>
         </is>
       </c>
       <c r="E233" s="19" t="inlineStr">
         <is>
-          <t>Argan Inc</t>
+          <t>PLDT Inc.</t>
         </is>
       </c>
       <c r="F233" s="26" t="inlineStr">
@@ -50324,12 +50324,12 @@
       </c>
       <c r="G233" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="H233" s="21" t="inlineStr">
         <is>
-          <t>Construction &amp; Engineering</t>
+          <t>Diversified Telecommunication Services</t>
         </is>
       </c>
       <c r="I233" s="16" t="inlineStr">
@@ -50338,7 +50338,7 @@
         </is>
       </c>
       <c r="J233" s="22" t="n">
-        <v>5804706816</v>
+        <v>4861255168</v>
       </c>
       <c r="K233" s="25" t="inlineStr">
         <is>
@@ -50346,21 +50346,21 @@
         </is>
       </c>
       <c r="L233" s="22" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="M233" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N233" s="21" t="inlineStr">
         <is>
-          <t>DeadOption, CashReinvest, LindyFCF, NoDilution, LindyGrowth, BuybackCo</t>
+          <t>NarrativeLag, CapitalReturner, NetCashReturner, LynchEV-GY, LigerLaggi</t>
         </is>
       </c>
       <c r="O233" s="24" t="n">
-        <v>0.4169910857151652</v>
+        <v>0.3425930168343006</v>
       </c>
       <c r="P233" s="24" t="n">
-        <v>0.45592386</v>
+        <v>0.4558514814</v>
       </c>
     </row>
     <row r="234" ht="16" customHeight="1">
@@ -63184,27 +63184,27 @@
       </c>
       <c r="D432" s="18" t="inlineStr">
         <is>
-          <t>UVRBF</t>
+          <t>WJRYY</t>
         </is>
       </c>
       <c r="E432" s="19" t="inlineStr">
         <is>
-          <t>Universal Robina Corporation</t>
+          <t>West Japan Railway Company</t>
         </is>
       </c>
       <c r="F432" s="26" t="inlineStr">
         <is>
-          <t>PH</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G432" s="21" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H432" s="21" t="inlineStr">
         <is>
-          <t>Food &amp; Staples Retailing</t>
+          <t>Road &amp; Rail</t>
         </is>
       </c>
       <c r="I432" s="16" t="inlineStr">
@@ -63213,7 +63213,7 @@
         </is>
       </c>
       <c r="J432" s="22" t="n">
-        <v>2129043200</v>
+        <v>8865032192</v>
       </c>
       <c r="K432" s="25" t="inlineStr">
         <is>
@@ -63221,21 +63221,21 @@
         </is>
       </c>
       <c r="L432" s="22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M432" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N432" s="21" t="inlineStr">
         <is>
-          <t>CapitalDiscipline, LynchEV-GY, LigerLaggingInflect</t>
+          <t>NarrativeLag, FixedCost+DemandShock, RegimeCyclical, Forensic-Understa</t>
         </is>
       </c>
       <c r="O432" s="24" t="n">
-        <v>0.3732668102239384</v>
+        <v>0.3684605316426148</v>
       </c>
       <c r="P432" s="24" t="n">
-        <v>0.4232844</v>
+        <v>0.4230068184</v>
       </c>
     </row>
     <row r="433" ht="16" customHeight="1">
@@ -63249,12 +63249,12 @@
       </c>
       <c r="D433" s="18" t="inlineStr">
         <is>
-          <t>WJRYY</t>
+          <t>WST</t>
         </is>
       </c>
       <c r="E433" s="19" t="inlineStr">
         <is>
-          <t>West Japan Railway Company</t>
+          <t>West Pharmaceutical Services, Inc.</t>
         </is>
       </c>
       <c r="F433" s="26" t="inlineStr">
@@ -63264,21 +63264,21 @@
       </c>
       <c r="G433" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="H433" s="21" t="inlineStr">
         <is>
-          <t>Road &amp; Rail</t>
+          <t>Health Care Equipment &amp; Supplies</t>
         </is>
       </c>
       <c r="I433" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="J433" s="22" t="n">
-        <v>8865032192</v>
+        <v>24366200832</v>
       </c>
       <c r="K433" s="25" t="inlineStr">
         <is>
@@ -63286,21 +63286,21 @@
         </is>
       </c>
       <c r="L433" s="22" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M433" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N433" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, RegimeCyclical, Forensic-Understa</t>
+          <t>LindyMargin, LindyFCF, NoDilution, BuybackCompounder, LargeCapQuality,</t>
         </is>
       </c>
       <c r="O433" s="24" t="n">
-        <v>0.3684605316426148</v>
+        <v>0.3807445036921761</v>
       </c>
       <c r="P433" s="24" t="n">
-        <v>0.4230068184</v>
+        <v>0.422991848</v>
       </c>
     </row>
     <row r="434" ht="16" customHeight="1">
@@ -63314,36 +63314,36 @@
       </c>
       <c r="D434" s="18" t="inlineStr">
         <is>
-          <t>WST</t>
+          <t>1961.T</t>
         </is>
       </c>
       <c r="E434" s="19" t="inlineStr">
         <is>
-          <t>West Pharmaceutical Services, Inc.</t>
+          <t>Sanki Engineering Co., Ltd.</t>
         </is>
       </c>
       <c r="F434" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G434" s="21" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H434" s="21" t="inlineStr">
         <is>
-          <t>Health Care Equipment &amp; Supplies</t>
+          <t>Construction &amp; Engineering</t>
         </is>
       </c>
       <c r="I434" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="J434" s="22" t="n">
-        <v>24366200832</v>
+        <v>2189614023.418341</v>
       </c>
       <c r="K434" s="25" t="inlineStr">
         <is>
@@ -63351,21 +63351,21 @@
         </is>
       </c>
       <c r="L434" s="22" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="M434" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N434" s="21" t="inlineStr">
         <is>
-          <t>LindyMargin, LindyFCF, NoDilution, BuybackCompounder, LargeCapQuality,</t>
+          <t xml:space="preserve">KPIThreshold, QuietCompounder, MidCapGARP, StrongCoverage, LynchPEGY, </t>
         </is>
       </c>
       <c r="O434" s="24" t="n">
-        <v>0.3807445036921761</v>
+        <v>0.3955252182554333</v>
       </c>
       <c r="P434" s="24" t="n">
-        <v>0.422991848</v>
+        <v>0.4226989644</v>
       </c>
     </row>
     <row r="435" ht="16" customHeight="1">
@@ -63379,36 +63379,36 @@
       </c>
       <c r="D435" s="18" t="inlineStr">
         <is>
-          <t>1961.T</t>
+          <t>PAAS.TO</t>
         </is>
       </c>
       <c r="E435" s="19" t="inlineStr">
         <is>
-          <t>Sanki Engineering Co., Ltd.</t>
+          <t>PAN AMERICAN SILVER CORP</t>
         </is>
       </c>
       <c r="F435" s="26" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G435" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H435" s="21" t="inlineStr">
         <is>
-          <t>Construction &amp; Engineering</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="I435" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="J435" s="22" t="n">
-        <v>2189614023.418341</v>
+        <v>20718569823.74561</v>
       </c>
       <c r="K435" s="25" t="inlineStr">
         <is>
@@ -63416,21 +63416,21 @@
         </is>
       </c>
       <c r="L435" s="22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M435" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N435" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">KPIThreshold, QuietCompounder, MidCapGARP, StrongCoverage, LynchPEGY, </t>
+          <t>FixedCost+DemandShock, RegimeCyclical, LargeCapQuality, MidCapGARP, St</t>
         </is>
       </c>
       <c r="O435" s="24" t="n">
-        <v>0.3955252182554333</v>
+        <v>0.4101897986043997</v>
       </c>
       <c r="P435" s="24" t="n">
-        <v>0.4226989644</v>
+        <v>0.4225874622</v>
       </c>
     </row>
     <row r="436" ht="16" customHeight="1">
@@ -63444,36 +63444,36 @@
       </c>
       <c r="D436" s="18" t="inlineStr">
         <is>
-          <t>PAAS.TO</t>
+          <t>LKQ</t>
         </is>
       </c>
       <c r="E436" s="19" t="inlineStr">
         <is>
-          <t>PAN AMERICAN SILVER CORP</t>
+          <t>LKQ Corporation</t>
         </is>
       </c>
       <c r="F436" s="26" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G436" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="H436" s="21" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Auto Components</t>
         </is>
       </c>
       <c r="I436" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="J436" s="22" t="n">
-        <v>20718569823.74561</v>
+        <v>6099880448</v>
       </c>
       <c r="K436" s="25" t="inlineStr">
         <is>
@@ -63481,21 +63481,21 @@
         </is>
       </c>
       <c r="L436" s="22" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="M436" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N436" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, RegimeCyclical, LargeCapQuality, MidCapGARP, St</t>
+          <t>NarrativeLag, LindyFCF, NoDilution, CapitalReturner, LowSBCQuality, Ge</t>
         </is>
       </c>
       <c r="O436" s="24" t="n">
-        <v>0.4101897986043997</v>
+        <v>0.3668171847414376</v>
       </c>
       <c r="P436" s="24" t="n">
-        <v>0.4225874622</v>
+        <v>0.4225728</v>
       </c>
     </row>
     <row r="437" ht="16" customHeight="1">
@@ -63509,36 +63509,36 @@
       </c>
       <c r="D437" s="18" t="inlineStr">
         <is>
-          <t>LKQ</t>
+          <t>B8O.F</t>
         </is>
       </c>
       <c r="E437" s="19" t="inlineStr">
         <is>
-          <t>LKQ Corporation</t>
+          <t>Yangzijiang Shipbuilding Holdings, Ltd.</t>
         </is>
       </c>
       <c r="F437" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G437" s="21" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H437" s="21" t="inlineStr">
         <is>
-          <t>Auto Components</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="I437" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="J437" s="22" t="n">
-        <v>6099880448</v>
+        <v>15013914247.77686</v>
       </c>
       <c r="K437" s="25" t="inlineStr">
         <is>
@@ -63546,21 +63546,21 @@
         </is>
       </c>
       <c r="L437" s="22" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M437" s="22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N437" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, LindyFCF, NoDilution, CapitalReturner, LowSBCQuality, Ge</t>
+          <t>CapitalDiscipline, OwnerOperator, LargeCapQuality, MidCapGARP, Weinste</t>
         </is>
       </c>
       <c r="O437" s="24" t="n">
-        <v>0.3668171847414376</v>
+        <v>0.4551581311869413</v>
       </c>
       <c r="P437" s="24" t="n">
-        <v>0.4225728</v>
+        <v>0.422511232</v>
       </c>
     </row>
     <row r="438" ht="16" customHeight="1">
@@ -63574,17 +63574,17 @@
       </c>
       <c r="D438" s="18" t="inlineStr">
         <is>
-          <t>B8O.F</t>
+          <t>AYI</t>
         </is>
       </c>
       <c r="E438" s="19" t="inlineStr">
         <is>
-          <t>Yangzijiang Shipbuilding Holdings, Ltd.</t>
+          <t>Acuity Brands, Inc.</t>
         </is>
       </c>
       <c r="F438" s="26" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G438" s="21" t="inlineStr">
@@ -63594,16 +63594,16 @@
       </c>
       <c r="H438" s="21" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Electrical Equipment</t>
         </is>
       </c>
       <c r="I438" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="J438" s="22" t="n">
-        <v>15013914247.77686</v>
+        <v>9548241920</v>
       </c>
       <c r="K438" s="25" t="inlineStr">
         <is>
@@ -63611,21 +63611,21 @@
         </is>
       </c>
       <c r="L438" s="22" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="M438" s="22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N438" s="21" t="inlineStr">
         <is>
-          <t>CapitalDiscipline, OwnerOperator, LargeCapQuality, MidCapGARP, Weinste</t>
+          <t>NarrativeLag, FixedCost+DemandShock, CashReinvest, LindyMargin, LindyF</t>
         </is>
       </c>
       <c r="O438" s="24" t="n">
-        <v>0.4551581311869413</v>
+        <v>0.3666860393161141</v>
       </c>
       <c r="P438" s="24" t="n">
-        <v>0.422511232</v>
+        <v>0.42242176</v>
       </c>
     </row>
     <row r="439" ht="16" customHeight="1">
@@ -63639,36 +63639,36 @@
       </c>
       <c r="D439" s="18" t="inlineStr">
         <is>
-          <t>AYI</t>
+          <t>3665.TW</t>
         </is>
       </c>
       <c r="E439" s="19" t="inlineStr">
         <is>
-          <t>Acuity Brands, Inc.</t>
+          <t>Bizlink Holding Inc.</t>
         </is>
       </c>
       <c r="F439" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G439" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H439" s="21" t="inlineStr">
         <is>
-          <t>Electrical Equipment</t>
+          <t>Technology Hardware, Storage &amp; Peripherals</t>
         </is>
       </c>
       <c r="I439" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="J439" s="22" t="n">
-        <v>9548241920</v>
+        <v>11586098094.62278</v>
       </c>
       <c r="K439" s="25" t="inlineStr">
         <is>
@@ -63676,21 +63676,21 @@
         </is>
       </c>
       <c r="L439" s="22" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="M439" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N439" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, CashReinvest, LindyMargin, LindyF</t>
+          <t>LynchPEGY, LynchEV-GY, XR-ReusableAssembler</t>
         </is>
       </c>
       <c r="O439" s="24" t="n">
-        <v>0.3666860393161141</v>
+        <v>0.429805796708685</v>
       </c>
       <c r="P439" s="24" t="n">
-        <v>0.42242176</v>
+        <v>0.4224132</v>
       </c>
     </row>
     <row r="440" ht="16" customHeight="1">
@@ -63704,36 +63704,36 @@
       </c>
       <c r="D440" s="18" t="inlineStr">
         <is>
-          <t>3665.TW</t>
+          <t>TWODY</t>
         </is>
       </c>
       <c r="E440" s="19" t="inlineStr">
         <is>
-          <t>Bizlink Holding Inc.</t>
+          <t>Taylor Wimpey plc</t>
         </is>
       </c>
       <c r="F440" s="26" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G440" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H440" s="21" t="inlineStr">
         <is>
-          <t>Technology Hardware, Storage &amp; Peripherals</t>
+          <t>Construction &amp; Engineering</t>
         </is>
       </c>
       <c r="I440" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="J440" s="22" t="n">
-        <v>11586098094.62278</v>
+        <v>3639735552</v>
       </c>
       <c r="K440" s="25" t="inlineStr">
         <is>
@@ -63741,21 +63741,21 @@
         </is>
       </c>
       <c r="L440" s="22" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M440" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N440" s="21" t="inlineStr">
         <is>
-          <t>LynchPEGY, LynchEV-GY, XR-ReusableAssembler</t>
+          <t>NarrativeLag, CapitalReturner, Cundill-DeepValue, StrongCoverage, Lync</t>
         </is>
       </c>
       <c r="O440" s="24" t="n">
-        <v>0.429805796708685</v>
+        <v>0.3901809834895145</v>
       </c>
       <c r="P440" s="24" t="n">
-        <v>0.4224132</v>
+        <v>0.4223788563999999</v>
       </c>
     </row>
     <row r="441" ht="16" customHeight="1">
@@ -63769,12 +63769,12 @@
       </c>
       <c r="D441" s="18" t="inlineStr">
         <is>
-          <t>TWODY</t>
+          <t>HDALF</t>
         </is>
       </c>
       <c r="E441" s="19" t="inlineStr">
         <is>
-          <t>Taylor Wimpey plc</t>
+          <t>Haidilao International Holding Ltd.</t>
         </is>
       </c>
       <c r="F441" s="26" t="inlineStr">
@@ -63784,12 +63784,12 @@
       </c>
       <c r="G441" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="H441" s="21" t="inlineStr">
         <is>
-          <t>Construction &amp; Engineering</t>
+          <t>Hotels, Restaurants &amp; Leisure</t>
         </is>
       </c>
       <c r="I441" s="16" t="inlineStr">
@@ -63798,7 +63798,7 @@
         </is>
       </c>
       <c r="J441" s="22" t="n">
-        <v>3639735552</v>
+        <v>7323992576</v>
       </c>
       <c r="K441" s="25" t="inlineStr">
         <is>
@@ -63806,21 +63806,21 @@
         </is>
       </c>
       <c r="L441" s="22" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M441" s="22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N441" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, CapitalReturner, Cundill-DeepValue, StrongCoverage, Lync</t>
+          <t>CapitalDiscipline, QuietCompounder, OwnerOperator, CapitalReturner, Ba</t>
         </is>
       </c>
       <c r="O441" s="24" t="n">
-        <v>0.3901809834895145</v>
+        <v>0.4129622445692864</v>
       </c>
       <c r="P441" s="24" t="n">
-        <v>0.4223788563999999</v>
+        <v>0.4222869091999999</v>
       </c>
     </row>
     <row r="442" ht="16" customHeight="1">
@@ -63834,27 +63834,27 @@
       </c>
       <c r="D442" s="18" t="inlineStr">
         <is>
-          <t>HDALF</t>
+          <t>003490.KS</t>
         </is>
       </c>
       <c r="E442" s="19" t="inlineStr">
         <is>
-          <t>Haidilao International Holding Ltd.</t>
+          <t>Korean Air Lines Co., Ltd.</t>
         </is>
       </c>
       <c r="F442" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G442" s="21" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H442" s="21" t="inlineStr">
         <is>
-          <t>Hotels, Restaurants &amp; Leisure</t>
+          <t>Airlines</t>
         </is>
       </c>
       <c r="I442" s="16" t="inlineStr">
@@ -63863,7 +63863,7 @@
         </is>
       </c>
       <c r="J442" s="22" t="n">
-        <v>7323992576</v>
+        <v>6972414965.038239</v>
       </c>
       <c r="K442" s="25" t="inlineStr">
         <is>
@@ -63871,21 +63871,21 @@
         </is>
       </c>
       <c r="L442" s="22" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M442" s="22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N442" s="21" t="inlineStr">
         <is>
-          <t>CapitalDiscipline, QuietCompounder, OwnerOperator, CapitalReturner, Ba</t>
+          <t>FixedCost+DemandShock, BalanceSheetReturn, Weinstein-Stage2, XR-Latent</t>
         </is>
       </c>
       <c r="O442" s="24" t="n">
-        <v>0.4129622445692864</v>
+        <v>0.4140500311836295</v>
       </c>
       <c r="P442" s="24" t="n">
-        <v>0.4222869091999999</v>
+        <v>0.4216142085</v>
       </c>
     </row>
     <row r="443" ht="16" customHeight="1">
@@ -63899,27 +63899,27 @@
       </c>
       <c r="D443" s="18" t="inlineStr">
         <is>
-          <t>003490.KS</t>
+          <t>SHMZF</t>
         </is>
       </c>
       <c r="E443" s="19" t="inlineStr">
         <is>
-          <t>Korean Air Lines Co., Ltd.</t>
+          <t>Shimadzu Corporation</t>
         </is>
       </c>
       <c r="F443" s="26" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G443" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H443" s="21" t="inlineStr">
         <is>
-          <t>Airlines</t>
+          <t>Electronic Equipment, Instruments &amp; Components</t>
         </is>
       </c>
       <c r="I443" s="16" t="inlineStr">
@@ -63928,7 +63928,7 @@
         </is>
       </c>
       <c r="J443" s="22" t="n">
-        <v>6972414965.038239</v>
+        <v>6749641728</v>
       </c>
       <c r="K443" s="25" t="inlineStr">
         <is>
@@ -63936,21 +63936,21 @@
         </is>
       </c>
       <c r="L443" s="22" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M443" s="22" t="n">
         <v>1</v>
       </c>
       <c r="N443" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, BalanceSheetReturn, Weinstein-Stage2, XR-Latent</t>
+          <t>MidCapGARP, StrongCoverage, LynchPEGY, Bottleneck-Chokepoint</t>
         </is>
       </c>
       <c r="O443" s="24" t="n">
-        <v>0.4140500311836295</v>
+        <v>0.4136022447447241</v>
       </c>
       <c r="P443" s="24" t="n">
-        <v>0.4216142085</v>
+        <v>0.4214896166000001</v>
       </c>
     </row>
     <row r="444" ht="16" customHeight="1">
@@ -63964,12 +63964,12 @@
       </c>
       <c r="D444" s="18" t="inlineStr">
         <is>
-          <t>SHMZF</t>
+          <t>BZZUF</t>
         </is>
       </c>
       <c r="E444" s="19" t="inlineStr">
         <is>
-          <t>Shimadzu Corporation</t>
+          <t>Buzzi Unicem S.p.A.</t>
         </is>
       </c>
       <c r="F444" s="26" t="inlineStr">
@@ -63979,12 +63979,12 @@
       </c>
       <c r="G444" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H444" s="21" t="inlineStr">
         <is>
-          <t>Electronic Equipment, Instruments &amp; Components</t>
+          <t>Construction Materials</t>
         </is>
       </c>
       <c r="I444" s="16" t="inlineStr">
@@ -63993,7 +63993,7 @@
         </is>
       </c>
       <c r="J444" s="22" t="n">
-        <v>6749641728</v>
+        <v>8472559104</v>
       </c>
       <c r="K444" s="25" t="inlineStr">
         <is>
@@ -64001,21 +64001,21 @@
         </is>
       </c>
       <c r="L444" s="22" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M444" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N444" s="21" t="inlineStr">
         <is>
-          <t>MidCapGARP, StrongCoverage, LynchPEGY, Bottleneck-Chokepoint</t>
+          <t>NarrativeLag, FixedCost+DemandShock, CapitalDiscipline, OwnerOperator,</t>
         </is>
       </c>
       <c r="O444" s="24" t="n">
-        <v>0.4136022447447241</v>
+        <v>0.395675285290647</v>
       </c>
       <c r="P444" s="24" t="n">
-        <v>0.4214896166000001</v>
+        <v>0.4214182072</v>
       </c>
     </row>
     <row r="445" ht="16" customHeight="1">
@@ -64029,12 +64029,12 @@
       </c>
       <c r="D445" s="18" t="inlineStr">
         <is>
-          <t>BZZUF</t>
+          <t>FRCOY</t>
         </is>
       </c>
       <c r="E445" s="19" t="inlineStr">
         <is>
-          <t>Buzzi Unicem S.p.A.</t>
+          <t>Fast Retailing Co., Ltd.</t>
         </is>
       </c>
       <c r="F445" s="26" t="inlineStr">
@@ -64044,21 +64044,21 @@
       </c>
       <c r="G445" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="H445" s="21" t="inlineStr">
         <is>
-          <t>Construction Materials</t>
+          <t>Textiles, Apparel &amp; Luxury Goods</t>
         </is>
       </c>
       <c r="I445" s="16" t="inlineStr">
         <is>
-          <t>Mid Cap</t>
+          <t>Large Cap</t>
         </is>
       </c>
       <c r="J445" s="22" t="n">
-        <v>8472559104</v>
+        <v>132621017088</v>
       </c>
       <c r="K445" s="25" t="inlineStr">
         <is>
@@ -64066,21 +64066,21 @@
         </is>
       </c>
       <c r="L445" s="22" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="M445" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N445" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, CapitalDiscipline, OwnerOperator,</t>
+          <t>LargeCapQuality, StrongCoverage, Bottleneck-Chokepoint</t>
         </is>
       </c>
       <c r="O445" s="24" t="n">
-        <v>0.395675285290647</v>
+        <v>0.4170385434067795</v>
       </c>
       <c r="P445" s="24" t="n">
-        <v>0.4214182072</v>
+        <v>0.421355</v>
       </c>
     </row>
     <row r="446" ht="16" customHeight="1">
@@ -64094,12 +64094,12 @@
       </c>
       <c r="D446" s="18" t="inlineStr">
         <is>
-          <t>FRCOY</t>
+          <t>TNET</t>
         </is>
       </c>
       <c r="E446" s="19" t="inlineStr">
         <is>
-          <t>Fast Retailing Co., Ltd.</t>
+          <t>Trinet Group, Inc.</t>
         </is>
       </c>
       <c r="F446" s="26" t="inlineStr">
@@ -64109,21 +64109,21 @@
       </c>
       <c r="G446" s="21" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="H446" s="21" t="inlineStr">
         <is>
-          <t>Textiles, Apparel &amp; Luxury Goods</t>
+          <t>Professional Services</t>
         </is>
       </c>
       <c r="I446" s="16" t="inlineStr">
         <is>
-          <t>Large Cap</t>
+          <t>Mid Cap</t>
         </is>
       </c>
       <c r="J446" s="22" t="n">
-        <v>132621017088</v>
+        <v>3030171648</v>
       </c>
       <c r="K446" s="25" t="inlineStr">
         <is>
@@ -64131,21 +64131,21 @@
         </is>
       </c>
       <c r="L446" s="22" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="M446" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N446" s="21" t="inlineStr">
         <is>
-          <t>LargeCapQuality, StrongCoverage, Bottleneck-Chokepoint</t>
+          <t>NarrativeLag, MidCapGARP, CapitalReturner, LowSBCQuality, BAB-Becoming</t>
         </is>
       </c>
       <c r="O446" s="24" t="n">
-        <v>0.4170385434067795</v>
+        <v>0.3666953187592925</v>
       </c>
       <c r="P446" s="24" t="n">
-        <v>0.421355</v>
+        <v>0.4213111916</v>
       </c>
     </row>
     <row r="447" ht="16" customHeight="1">
@@ -64159,27 +64159,27 @@
       </c>
       <c r="D447" s="18" t="inlineStr">
         <is>
-          <t>TNET</t>
+          <t>GGBR4.SA</t>
         </is>
       </c>
       <c r="E447" s="19" t="inlineStr">
         <is>
-          <t>Trinet Group, Inc.</t>
+          <t>Gerdau S.A.</t>
         </is>
       </c>
       <c r="F447" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="G447" s="21" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H447" s="21" t="inlineStr">
         <is>
-          <t>Professional Services</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="I447" s="16" t="inlineStr">
@@ -64188,7 +64188,7 @@
         </is>
       </c>
       <c r="J447" s="22" t="n">
-        <v>3030171648</v>
+        <v>9842497539.897947</v>
       </c>
       <c r="K447" s="25" t="inlineStr">
         <is>
@@ -64196,21 +64196,21 @@
         </is>
       </c>
       <c r="L447" s="22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M447" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N447" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, MidCapGARP, CapitalReturner, LowSBCQuality, BAB-Becoming</t>
+          <t>Weinstein-Stage2, BAB-Becoming, LynchPEGY, Forensic-PayoutConfirmed, F</t>
         </is>
       </c>
       <c r="O447" s="24" t="n">
-        <v>0.3666953187592925</v>
+        <v>0.3918790758786376</v>
       </c>
       <c r="P447" s="24" t="n">
-        <v>0.4213111916</v>
+        <v>0.4210889270000001</v>
       </c>
     </row>
     <row r="448" ht="16" customHeight="1">
@@ -64224,27 +64224,27 @@
       </c>
       <c r="D448" s="18" t="inlineStr">
         <is>
-          <t>GGBR4.SA</t>
+          <t>0285.HK</t>
         </is>
       </c>
       <c r="E448" s="19" t="inlineStr">
         <is>
-          <t>Gerdau S.A.</t>
+          <t>BYD Electronic (International) Company Limited</t>
         </is>
       </c>
       <c r="F448" s="26" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G448" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H448" s="21" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Communications Equipment</t>
         </is>
       </c>
       <c r="I448" s="16" t="inlineStr">
@@ -64253,7 +64253,7 @@
         </is>
       </c>
       <c r="J448" s="22" t="n">
-        <v>9842497539.897947</v>
+        <v>6838612255.101865</v>
       </c>
       <c r="K448" s="25" t="inlineStr">
         <is>
@@ -64261,21 +64261,21 @@
         </is>
       </c>
       <c r="L448" s="22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M448" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N448" s="21" t="inlineStr">
         <is>
-          <t>Weinstein-Stage2, BAB-Becoming, LynchPEGY, Forensic-PayoutConfirmed, F</t>
+          <t>NarrativeLag, CapitalDiscipline, OwnerOperator, StrongCoverage, Temple</t>
         </is>
       </c>
       <c r="O448" s="24" t="n">
-        <v>0.3918790758786376</v>
+        <v>0.3813040132620671</v>
       </c>
       <c r="P448" s="24" t="n">
-        <v>0.4210889270000001</v>
+        <v>0.420894225</v>
       </c>
     </row>
     <row r="449" ht="16" customHeight="1">
@@ -64289,27 +64289,27 @@
       </c>
       <c r="D449" s="18" t="inlineStr">
         <is>
-          <t>0285.HK</t>
+          <t>MZTI</t>
         </is>
       </c>
       <c r="E449" s="19" t="inlineStr">
         <is>
-          <t>BYD Electronic (International) Company Limited</t>
+          <t>The Marzetti Company Common Stock</t>
         </is>
       </c>
       <c r="F449" s="26" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G449" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="H449" s="21" t="inlineStr">
         <is>
-          <t>Communications Equipment</t>
+          <t>Food &amp; Staples Retailing</t>
         </is>
       </c>
       <c r="I449" s="16" t="inlineStr">
@@ -64318,7 +64318,7 @@
         </is>
       </c>
       <c r="J449" s="22" t="n">
-        <v>6838612255.101865</v>
+        <v>2839628544</v>
       </c>
       <c r="K449" s="25" t="inlineStr">
         <is>
@@ -64326,21 +64326,21 @@
         </is>
       </c>
       <c r="L449" s="22" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M449" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N449" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, CapitalDiscipline, OwnerOperator, StrongCoverage, Temple</t>
+          <t xml:space="preserve">NarrativeLag, CapitalDiscipline, CashReinvest, LindyMargin, LindyFCF, </t>
         </is>
       </c>
       <c r="O449" s="24" t="n">
-        <v>0.3813040132620671</v>
+        <v>0.3779559453679549</v>
       </c>
       <c r="P449" s="24" t="n">
-        <v>0.420894225</v>
+        <v>0.4206418560000001</v>
       </c>
     </row>
     <row r="450" ht="16" customHeight="1">
@@ -64354,12 +64354,12 @@
       </c>
       <c r="D450" s="18" t="inlineStr">
         <is>
-          <t>MZTI</t>
+          <t>PJT</t>
         </is>
       </c>
       <c r="E450" s="19" t="inlineStr">
         <is>
-          <t>The Marzetti Company Common Stock</t>
+          <t>Pjt Partners Inc.</t>
         </is>
       </c>
       <c r="F450" s="26" t="inlineStr">
@@ -64369,12 +64369,12 @@
       </c>
       <c r="G450" s="21" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="H450" s="21" t="inlineStr">
         <is>
-          <t>Food &amp; Staples Retailing</t>
+          <t>Capital Markets</t>
         </is>
       </c>
       <c r="I450" s="16" t="inlineStr">
@@ -64383,29 +64383,29 @@
         </is>
       </c>
       <c r="J450" s="22" t="n">
-        <v>2839628544</v>
-      </c>
-      <c r="K450" s="25" t="inlineStr">
-        <is>
-          <t>UNRESEARCHED</t>
+        <v>6952289792</v>
+      </c>
+      <c r="K450" s="23" t="inlineStr">
+        <is>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="L450" s="22" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="M450" s="22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N450" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">NarrativeLag, CapitalDiscipline, CashReinvest, LindyMargin, LindyFCF, </t>
+          <t>Weinstein-Stage2, LynchPEGY, AsleepAtWheel-Beats, AsleepUnrerated-Beat</t>
         </is>
       </c>
       <c r="O450" s="24" t="n">
-        <v>0.3779559453679549</v>
+        <v>0.3319382175059425</v>
       </c>
       <c r="P450" s="24" t="n">
-        <v>0.4206418560000001</v>
+        <v>0.42063232</v>
       </c>
     </row>
     <row r="451" ht="16" customHeight="1">
@@ -64419,27 +64419,27 @@
       </c>
       <c r="D451" s="18" t="inlineStr">
         <is>
-          <t>PJT</t>
+          <t>SCT.L</t>
         </is>
       </c>
       <c r="E451" s="19" t="inlineStr">
         <is>
-          <t>Pjt Partners Inc.</t>
+          <t>Softcat plc</t>
         </is>
       </c>
       <c r="F451" s="26" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="G451" s="21" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H451" s="21" t="inlineStr">
         <is>
-          <t>Capital Markets</t>
+          <t>IT Services</t>
         </is>
       </c>
       <c r="I451" s="16" t="inlineStr">
@@ -64448,29 +64448,29 @@
         </is>
       </c>
       <c r="J451" s="22" t="n">
-        <v>6952289792</v>
-      </c>
-      <c r="K451" s="23" t="inlineStr">
-        <is>
-          <t>GREEN</t>
+        <v>4874979959.599915</v>
+      </c>
+      <c r="K451" s="25" t="inlineStr">
+        <is>
+          <t>UNRESEARCHED</t>
         </is>
       </c>
       <c r="L451" s="22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M451" s="22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N451" s="21" t="inlineStr">
         <is>
-          <t>Weinstein-Stage2, LynchPEGY, AsleepAtWheel-Beats, AsleepUnrerated-Beat</t>
+          <t>NarrativeLag, CapitalDiscipline, Weinstein-Stage2, Kullamagi-Breakout,</t>
         </is>
       </c>
       <c r="O451" s="24" t="n">
-        <v>0.3319382175059425</v>
+        <v>0.4154131964770285</v>
       </c>
       <c r="P451" s="24" t="n">
-        <v>0.42063232</v>
+        <v>0.420606</v>
       </c>
     </row>
     <row r="452" ht="16" customHeight="1">
@@ -64484,27 +64484,27 @@
       </c>
       <c r="D452" s="18" t="inlineStr">
         <is>
-          <t>SCT.L</t>
+          <t>TXG.TO</t>
         </is>
       </c>
       <c r="E452" s="19" t="inlineStr">
         <is>
-          <t>Softcat plc</t>
+          <t>Torex Gold Resources Inc.</t>
         </is>
       </c>
       <c r="F452" s="26" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G452" s="21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="H452" s="21" t="inlineStr">
         <is>
-          <t>IT Services</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="I452" s="16" t="inlineStr">
@@ -64513,7 +64513,7 @@
         </is>
       </c>
       <c r="J452" s="22" t="n">
-        <v>4874979959.599915</v>
+        <v>4630293608.316376</v>
       </c>
       <c r="K452" s="25" t="inlineStr">
         <is>
@@ -64521,21 +64521,21 @@
         </is>
       </c>
       <c r="L452" s="22" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M452" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N452" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, CapitalDiscipline, Weinstein-Stage2, Kullamagi-Breakout,</t>
+          <t>KPIThreshold, MidCapGARP, StrongCoverage, LynchPEGY, LynchEV-GY, Foren</t>
         </is>
       </c>
       <c r="O452" s="24" t="n">
-        <v>0.4154131964770285</v>
+        <v>0.3750613720400396</v>
       </c>
       <c r="P452" s="24" t="n">
-        <v>0.420606</v>
+        <v>0.42059353</v>
       </c>
     </row>
     <row r="453" ht="16" customHeight="1">
@@ -64549,27 +64549,27 @@
       </c>
       <c r="D453" s="18" t="inlineStr">
         <is>
-          <t>TXG.TO</t>
+          <t>UVRBF</t>
         </is>
       </c>
       <c r="E453" s="19" t="inlineStr">
         <is>
-          <t>Torex Gold Resources Inc.</t>
+          <t>Universal Robina Corporation</t>
         </is>
       </c>
       <c r="F453" s="26" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>PH</t>
         </is>
       </c>
       <c r="G453" s="21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="H453" s="21" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Food &amp; Staples Retailing</t>
         </is>
       </c>
       <c r="I453" s="16" t="inlineStr">
@@ -64578,7 +64578,7 @@
         </is>
       </c>
       <c r="J453" s="22" t="n">
-        <v>4630293608.316376</v>
+        <v>2129043200</v>
       </c>
       <c r="K453" s="25" t="inlineStr">
         <is>
@@ -64586,21 +64586,21 @@
         </is>
       </c>
       <c r="L453" s="22" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M453" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N453" s="21" t="inlineStr">
         <is>
-          <t>KPIThreshold, MidCapGARP, StrongCoverage, LynchPEGY, LynchEV-GY, Foren</t>
+          <t>CapitalDiscipline, LynchEV-GY, LigerLaggingInflect</t>
         </is>
       </c>
       <c r="O453" s="24" t="n">
-        <v>0.3750613720400396</v>
+        <v>0.3732668102239384</v>
       </c>
       <c r="P453" s="24" t="n">
-        <v>0.42059353</v>
+        <v>0.420462504</v>
       </c>
     </row>
     <row r="454" ht="16" customHeight="1">

--- a/nms_multibagger_candidates_midcap_plus.xlsx
+++ b/nms_multibagger_candidates_midcap_plus.xlsx
@@ -9982,7 +9982,7 @@
         </is>
       </c>
       <c r="L142" s="22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M142" s="22" t="n">
         <v>5</v>
@@ -27253,7 +27253,7 @@
         </is>
       </c>
       <c r="L91" s="22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M91" s="22" t="n">
         <v>3</v>
@@ -51016,7 +51016,7 @@
         </is>
       </c>
       <c r="L191" s="22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M191" s="22" t="n">
         <v>2</v>
@@ -59093,7 +59093,7 @@
         </is>
       </c>
       <c r="L316" s="22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M316" s="22" t="n">
         <v>2</v>
@@ -63054,7 +63054,7 @@
         </is>
       </c>
       <c r="L377" s="22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M377" s="22" t="n">
         <v>2</v>

--- a/nms_multibagger_candidates_midcap_plus.xlsx
+++ b/nms_multibagger_candidates_midcap_plus.xlsx
@@ -658,7 +658,7 @@
     <row r="9" ht="22" customHeight="1">
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>This shortlist filters the 5,176 multibagger candidates in the NMS sub-universe (mcap &lt; ~$2B, RED-verdicted names excluded). Each name is assigned a conviction tier based on its archetype-count, inflection-cluster density and asymmetry score. STRICT (301) = 5+ archetypes firing AND 3+ inflection signals AND asymmetry &gt;= 0.40. STRONG (238) = 3+ archetypes AND 3+ inflection signals AND asymmetry &gt;= 0.35. CANDIDATE (4637) = the broader funnel - 3+ archetypes or 4+ inflection signals at asymmetry &gt;= 0.35. (Multi-archetype gates are calibrated to the current 69-archetype taxonomy.) Within each tier, names are ranked by confirmed entry-today asymmetry (asymmetry_score x qual_multiplier x post-rally factor x confirmation multiplier (1 + 0.20 x confirm_overall + 0.10 x buyback_score)).</t>
+          <t>This shortlist filters the 5,213 multibagger candidates in the NMS sub-universe (mcap &lt; ~$2B, RED-verdicted names excluded). Each name is assigned a conviction tier based on its archetype-count, inflection-cluster density and asymmetry score. STRICT (301) = 5+ archetypes firing AND 3+ inflection signals AND asymmetry &gt;= 0.40. STRONG (238) = 3+ archetypes AND 3+ inflection signals AND asymmetry &gt;= 0.35. CANDIDATE (4674) = the broader funnel - 3+ archetypes or 4+ inflection signals at asymmetry &gt;= 0.35. (Multi-archetype gates are calibrated to the current 69-archetype taxonomy.) Within each tier, names are ranked by confirmed entry-today asymmetry (asymmetry_score x qual_multiplier x post-rally factor x confirmation multiplier (1 + 0.20 x confirm_overall + 0.10 x buyback_score)).</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>4,637</t>
+          <t>4,674</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="L7" s="22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M7" s="22" t="n">
         <v>4</v>
@@ -1304,7 +1304,7 @@
         </is>
       </c>
       <c r="L8" s="22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M8" s="22" t="n">
         <v>4</v>
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="L14" s="22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M14" s="22" t="n">
         <v>4</v>
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="L18" s="22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M18" s="22" t="n">
         <v>6</v>
@@ -2141,7 +2141,7 @@
         </is>
       </c>
       <c r="L21" s="22" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M21" s="22" t="n">
         <v>3</v>
@@ -2726,7 +2726,7 @@
         </is>
       </c>
       <c r="L30" s="22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M30" s="22" t="n">
         <v>6</v>
@@ -3571,7 +3571,7 @@
         </is>
       </c>
       <c r="L43" s="22" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M43" s="22" t="n">
         <v>3</v>
@@ -4668,7 +4668,7 @@
         </is>
       </c>
       <c r="L60" s="22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M60" s="22" t="n">
         <v>5</v>
@@ -4985,7 +4985,7 @@
         </is>
       </c>
       <c r="L65" s="22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M65" s="22" t="n">
         <v>3</v>
@@ -5826,7 +5826,7 @@
         </is>
       </c>
       <c r="L78" s="22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M78" s="22" t="n">
         <v>4</v>
@@ -5956,7 +5956,7 @@
         </is>
       </c>
       <c r="L80" s="22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M80" s="22" t="n">
         <v>4</v>
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c r="L98" s="22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M98" s="22" t="n">
         <v>5</v>
@@ -7256,7 +7256,7 @@
         </is>
       </c>
       <c r="L100" s="22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M100" s="22" t="n">
         <v>4</v>
@@ -8292,7 +8292,7 @@
         </is>
       </c>
       <c r="L116" s="22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M116" s="22" t="n">
         <v>3</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="L121" s="22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M121" s="22" t="n">
         <v>3</v>
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="L122" s="22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M122" s="22" t="n">
         <v>3</v>
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="L123" s="22" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M123" s="22" t="n">
         <v>3</v>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="L132" s="22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M132" s="22" t="n">
         <v>3</v>
@@ -9397,7 +9397,7 @@
         </is>
       </c>
       <c r="L133" s="22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M133" s="22" t="n">
         <v>4</v>
@@ -9462,7 +9462,7 @@
         </is>
       </c>
       <c r="L134" s="22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M134" s="22" t="n">
         <v>3</v>
@@ -10047,7 +10047,7 @@
         </is>
       </c>
       <c r="L143" s="22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M143" s="22" t="n">
         <v>3</v>
@@ -10177,7 +10177,7 @@
         </is>
       </c>
       <c r="L145" s="22" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M145" s="22" t="n">
         <v>4</v>
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="L148" s="22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M148" s="22" t="n">
         <v>4</v>
@@ -11469,7 +11469,7 @@
         </is>
       </c>
       <c r="L165" s="22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M165" s="22" t="n">
         <v>3</v>
@@ -11851,7 +11851,7 @@
         </is>
       </c>
       <c r="L171" s="22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M171" s="22" t="n">
         <v>5</v>
@@ -11916,7 +11916,7 @@
         </is>
       </c>
       <c r="L172" s="22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M172" s="22" t="n">
         <v>3</v>
@@ -15609,7 +15609,7 @@
         </is>
       </c>
       <c r="L229" s="22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M229" s="22" t="n">
         <v>5</v>
@@ -17356,7 +17356,7 @@
         </is>
       </c>
       <c r="L256" s="22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M256" s="22" t="n">
         <v>3</v>
@@ -18514,7 +18514,7 @@
         </is>
       </c>
       <c r="L274" s="22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M274" s="22" t="n">
         <v>3</v>
@@ -19229,7 +19229,7 @@
         </is>
       </c>
       <c r="L285" s="22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M285" s="22" t="n">
         <v>5</v>
@@ -19424,7 +19424,7 @@
         </is>
       </c>
       <c r="L288" s="22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M288" s="22" t="n">
         <v>4</v>
@@ -19554,7 +19554,7 @@
         </is>
       </c>
       <c r="L290" s="22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M290" s="22" t="n">
         <v>4</v>
@@ -19684,7 +19684,7 @@
         </is>
       </c>
       <c r="L292" s="22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M292" s="22" t="n">
         <v>4</v>
@@ -19940,7 +19940,7 @@
         </is>
       </c>
       <c r="L296" s="22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M296" s="22" t="n">
         <v>3</v>
@@ -20135,7 +20135,7 @@
         </is>
       </c>
       <c r="L299" s="22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M299" s="22" t="n">
         <v>3</v>
@@ -20395,7 +20395,7 @@
         </is>
       </c>
       <c r="L303" s="22" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M303" s="22" t="n">
         <v>4</v>
@@ -21699,7 +21699,7 @@
         </is>
       </c>
       <c r="L20" s="22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M20" s="22" t="n">
         <v>3</v>
@@ -21829,7 +21829,7 @@
         </is>
       </c>
       <c r="L22" s="22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M22" s="22" t="n">
         <v>3</v>
@@ -21959,7 +21959,7 @@
         </is>
       </c>
       <c r="L24" s="22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M24" s="22" t="n">
         <v>3</v>
@@ -22853,7 +22853,7 @@
         </is>
       </c>
       <c r="L38" s="22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M38" s="22" t="n">
         <v>3</v>
@@ -23178,7 +23178,7 @@
         </is>
       </c>
       <c r="L43" s="22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M43" s="22" t="n">
         <v>3</v>
@@ -23426,7 +23426,7 @@
         </is>
       </c>
       <c r="L47" s="22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M47" s="22" t="n">
         <v>4</v>
@@ -23621,7 +23621,7 @@
         </is>
       </c>
       <c r="L50" s="22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M50" s="22" t="n">
         <v>3</v>
@@ -24076,7 +24076,7 @@
         </is>
       </c>
       <c r="L57" s="22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M57" s="22" t="n">
         <v>4</v>
@@ -24133,7 +24133,7 @@
         </is>
       </c>
       <c r="L58" s="22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M58" s="22" t="n">
         <v>3</v>
@@ -24913,7 +24913,7 @@
         </is>
       </c>
       <c r="L70" s="22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M70" s="22" t="n">
         <v>3</v>
@@ -25043,7 +25043,7 @@
         </is>
       </c>
       <c r="L72" s="22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M72" s="22" t="n">
         <v>3</v>
@@ -25819,7 +25819,7 @@
         </is>
       </c>
       <c r="L84" s="22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M84" s="22" t="n">
         <v>3</v>
@@ -25884,7 +25884,7 @@
         </is>
       </c>
       <c r="L85" s="22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M85" s="22" t="n">
         <v>4</v>
@@ -26079,7 +26079,7 @@
         </is>
       </c>
       <c r="L88" s="22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M88" s="22" t="n">
         <v>3</v>
@@ -26404,7 +26404,7 @@
         </is>
       </c>
       <c r="L93" s="22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M93" s="22" t="n">
         <v>3</v>
@@ -27371,7 +27371,7 @@
         </is>
       </c>
       <c r="L108" s="22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M108" s="22" t="n">
         <v>3</v>
@@ -27887,7 +27887,7 @@
         </is>
       </c>
       <c r="L116" s="22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M116" s="22" t="n">
         <v>4</v>
@@ -29053,7 +29053,7 @@
         </is>
       </c>
       <c r="L134" s="22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M134" s="22" t="n">
         <v>5</v>
@@ -29443,7 +29443,7 @@
         </is>
       </c>
       <c r="L140" s="22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M140" s="22" t="n">
         <v>3</v>
@@ -30475,7 +30475,7 @@
         </is>
       </c>
       <c r="L156" s="22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M156" s="22" t="n">
         <v>3</v>
@@ -30930,7 +30930,7 @@
         </is>
       </c>
       <c r="L163" s="22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M163" s="22" t="n">
         <v>5</v>
@@ -33526,7 +33526,7 @@
         </is>
       </c>
       <c r="L203" s="22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M203" s="22" t="n">
         <v>3</v>
@@ -34111,7 +34111,7 @@
         </is>
       </c>
       <c r="L212" s="22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M212" s="22" t="n">
         <v>3</v>
@@ -34891,7 +34891,7 @@
         </is>
       </c>
       <c r="L224" s="22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M224" s="22" t="n">
         <v>3</v>
@@ -34956,7 +34956,7 @@
         </is>
       </c>
       <c r="L225" s="22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M225" s="22" t="n">
         <v>4</v>
@@ -35147,7 +35147,7 @@
         </is>
       </c>
       <c r="L228" s="22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M228" s="22" t="n">
         <v>3</v>
@@ -35212,7 +35212,7 @@
         </is>
       </c>
       <c r="L229" s="22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M229" s="22" t="n">
         <v>3</v>
@@ -35472,7 +35472,7 @@
         </is>
       </c>
       <c r="L233" s="22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M233" s="22" t="n">
         <v>4</v>
@@ -35602,7 +35602,7 @@
         </is>
       </c>
       <c r="L235" s="22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M235" s="22" t="n">
         <v>4</v>
@@ -35667,7 +35667,7 @@
         </is>
       </c>
       <c r="L236" s="22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M236" s="22" t="n">
         <v>4</v>
@@ -37686,7 +37686,7 @@
         </is>
       </c>
       <c r="L27" s="22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M27" s="22" t="n">
         <v>1</v>
@@ -38653,7 +38653,7 @@
         </is>
       </c>
       <c r="L42" s="22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M42" s="22" t="n">
         <v>2</v>
@@ -41428,7 +41428,7 @@
         </is>
       </c>
       <c r="L85" s="22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M85" s="22" t="n">
         <v>2</v>
@@ -41619,7 +41619,7 @@
         </is>
       </c>
       <c r="L88" s="22" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M88" s="22" t="n">
         <v>2</v>
@@ -43809,7 +43809,7 @@
         </is>
       </c>
       <c r="L122" s="22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M122" s="22" t="n">
         <v>2</v>
@@ -43874,7 +43874,7 @@
         </is>
       </c>
       <c r="L123" s="22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M123" s="22" t="n">
         <v>2</v>
@@ -44004,7 +44004,7 @@
         </is>
       </c>
       <c r="L125" s="22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M125" s="22" t="n">
         <v>1</v>
@@ -44329,7 +44329,7 @@
         </is>
       </c>
       <c r="L130" s="22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M130" s="22" t="n">
         <v>1</v>
@@ -44589,7 +44589,7 @@
         </is>
       </c>
       <c r="L134" s="22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M134" s="22" t="n">
         <v>2</v>
@@ -45239,7 +45239,7 @@
         </is>
       </c>
       <c r="L144" s="22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M144" s="22" t="n">
         <v>2</v>
@@ -45564,7 +45564,7 @@
         </is>
       </c>
       <c r="L149" s="22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M149" s="22" t="n">
         <v>1</v>
@@ -45694,7 +45694,7 @@
         </is>
       </c>
       <c r="L151" s="22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M151" s="22" t="n">
         <v>2</v>
@@ -46409,7 +46409,7 @@
         </is>
       </c>
       <c r="L162" s="22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M162" s="22" t="n">
         <v>1</v>
@@ -46604,7 +46604,7 @@
         </is>
       </c>
       <c r="L165" s="22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M165" s="22" t="n">
         <v>1</v>
@@ -47120,7 +47120,7 @@
         </is>
       </c>
       <c r="L173" s="22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M173" s="22" t="n">
         <v>1</v>
@@ -47445,7 +47445,7 @@
         </is>
       </c>
       <c r="L178" s="22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M178" s="22" t="n">
         <v>0</v>
@@ -47575,7 +47575,7 @@
         </is>
       </c>
       <c r="L180" s="22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M180" s="22" t="n">
         <v>2</v>
@@ -48412,7 +48412,7 @@
         </is>
       </c>
       <c r="L193" s="22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M193" s="22" t="n">
         <v>1</v>
@@ -49318,7 +49318,7 @@
         </is>
       </c>
       <c r="L207" s="22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M207" s="22" t="n">
         <v>2</v>
@@ -49968,7 +49968,7 @@
         </is>
       </c>
       <c r="L217" s="22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M217" s="22" t="n">
         <v>2</v>
@@ -50163,7 +50163,7 @@
         </is>
       </c>
       <c r="L220" s="22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M220" s="22" t="n">
         <v>2</v>
@@ -50293,7 +50293,7 @@
         </is>
       </c>
       <c r="L222" s="22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M222" s="22" t="n">
         <v>1</v>
@@ -50943,7 +50943,7 @@
         </is>
       </c>
       <c r="L232" s="22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M232" s="22" t="n">
         <v>1</v>
@@ -52101,7 +52101,7 @@
         </is>
       </c>
       <c r="L250" s="22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M250" s="22" t="n">
         <v>2</v>
@@ -53389,7 +53389,7 @@
         </is>
       </c>
       <c r="L270" s="22" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M270" s="22" t="n">
         <v>1</v>
@@ -54612,7 +54612,7 @@
         </is>
       </c>
       <c r="L289" s="22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M289" s="22" t="n">
         <v>1</v>
@@ -54868,7 +54868,7 @@
         </is>
       </c>
       <c r="L293" s="22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M293" s="22" t="n">
         <v>2</v>
@@ -54933,7 +54933,7 @@
         </is>
       </c>
       <c r="L294" s="22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M294" s="22" t="n">
         <v>2</v>
@@ -55063,7 +55063,7 @@
         </is>
       </c>
       <c r="L296" s="22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M296" s="22" t="n">
         <v>2</v>
@@ -55583,7 +55583,7 @@
         </is>
       </c>
       <c r="L304" s="22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M304" s="22" t="n">
         <v>1</v>
@@ -57269,7 +57269,7 @@
         </is>
       </c>
       <c r="L330" s="22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M330" s="22" t="n">
         <v>2</v>
@@ -57594,7 +57594,7 @@
         </is>
       </c>
       <c r="L335" s="22" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M335" s="22" t="n">
         <v>2</v>
@@ -57919,7 +57919,7 @@
         </is>
       </c>
       <c r="L340" s="22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M340" s="22" t="n">
         <v>2</v>
@@ -58374,7 +58374,7 @@
         </is>
       </c>
       <c r="L347" s="22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M347" s="22" t="n">
         <v>1</v>
@@ -58504,7 +58504,7 @@
         </is>
       </c>
       <c r="L349" s="22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M349" s="22" t="n">
         <v>2</v>
@@ -58634,7 +58634,7 @@
         </is>
       </c>
       <c r="L351" s="22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M351" s="22" t="n">
         <v>2</v>
@@ -59731,7 +59731,7 @@
         </is>
       </c>
       <c r="L368" s="22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M368" s="22" t="n">
         <v>1</v>
@@ -60962,7 +60962,7 @@
         </is>
       </c>
       <c r="L387" s="22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M387" s="22" t="n">
         <v>1</v>
@@ -61539,7 +61539,7 @@
         </is>
       </c>
       <c r="L396" s="22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M396" s="22" t="n">
         <v>2</v>
@@ -63282,7 +63282,7 @@
         </is>
       </c>
       <c r="L423" s="22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M423" s="22" t="n">
         <v>0</v>
@@ -63993,7 +63993,7 @@
         </is>
       </c>
       <c r="L434" s="22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M434" s="22" t="n">
         <v>2</v>
@@ -66138,7 +66138,7 @@
         </is>
       </c>
       <c r="L467" s="22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M467" s="22" t="n">
         <v>2</v>
@@ -68340,7 +68340,7 @@
         </is>
       </c>
       <c r="L501" s="22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M501" s="22" t="n">
         <v>0</v>
@@ -68470,7 +68470,7 @@
         </is>
       </c>
       <c r="L503" s="22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M503" s="22" t="n">
         <v>2</v>

--- a/nms_multibagger_candidates_midcap_plus.xlsx
+++ b/nms_multibagger_candidates_midcap_plus.xlsx
@@ -658,7 +658,7 @@
     <row r="9" ht="22" customHeight="1">
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>This shortlist filters the 4,914 multibagger candidates in the NMS sub-universe (mcap &lt; ~$2B, RED-verdicted names excluded). Each name is assigned a conviction tier based on its archetype-count, inflection-cluster density and asymmetry score. STRICT (261) = 5+ archetypes firing AND 3+ inflection signals AND asymmetry &gt;= 0.40. STRONG (252) = 3+ archetypes AND 3+ inflection signals AND asymmetry &gt;= 0.35. CANDIDATE (4401) = the broader funnel - 3+ archetypes or 4+ inflection signals at asymmetry &gt;= 0.35. (Multi-archetype gates are calibrated to the current 69-archetype taxonomy.) Within each tier, names are ranked by confirmed entry-today asymmetry (asymmetry_score x qual_multiplier x post-rally factor x confirmation multiplier (1 + 0.20 x confirm_overall + 0.10 x buyback_score)).</t>
+          <t>This shortlist filters the 4,915 multibagger candidates in the NMS sub-universe (mcap &lt; ~$2B, RED-verdicted names excluded). Each name is assigned a conviction tier based on its archetype-count, inflection-cluster density and asymmetry score. STRICT (261) = 5+ archetypes firing AND 3+ inflection signals AND asymmetry &gt;= 0.40. STRONG (252) = 3+ archetypes AND 3+ inflection signals AND asymmetry &gt;= 0.35. CANDIDATE (4402) = the broader funnel - 3+ archetypes or 4+ inflection signals at asymmetry &gt;= 0.35. (Multi-archetype gates are calibrated to the current 69-archetype taxonomy.) Within each tier, names are ranked by confirmed entry-today asymmetry (asymmetry_score x qual_multiplier x post-rally factor x confirmation multiplier (1 + 0.20 x confirm_overall + 0.10 x buyback_score)).</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>4,401</t>
+          <t>4,402</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
@@ -1369,14 +1369,14 @@
         </is>
       </c>
       <c r="L9" s="22" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M9" s="22" t="n">
         <v>6</v>
       </c>
       <c r="N9" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, DerateThroughGrowth, CapitalDiscipline, DeadOption, KPIT</t>
+          <t>PSIX, NarrativeLag, DerateThroughGrowth, CapitalDiscipline, DeadOption</t>
         </is>
       </c>
       <c r="O9" s="24" t="n">
@@ -3376,14 +3376,14 @@
         </is>
       </c>
       <c r="L40" s="22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M40" s="22" t="n">
         <v>5</v>
       </c>
       <c r="N40" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, DerateThroughGrowth, FixedCost+DemandShock, RegimeCyclic</t>
+          <t>PSIX, NarrativeLag, DerateThroughGrowth, FixedCost+DemandShock, Regime</t>
         </is>
       </c>
       <c r="O40" s="24" t="n">
@@ -3701,14 +3701,14 @@
         </is>
       </c>
       <c r="L45" s="22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M45" s="22" t="n">
         <v>6</v>
       </c>
       <c r="N45" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, DerateThroughGrowth, FixedCost+DemandShock, RegimeCyclic</t>
+          <t>PSIX, NarrativeLag, DerateThroughGrowth, FixedCost+DemandShock, Regime</t>
         </is>
       </c>
       <c r="O45" s="24" t="n">
@@ -4985,14 +4985,14 @@
         </is>
       </c>
       <c r="L65" s="22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M65" s="22" t="n">
         <v>3</v>
       </c>
       <c r="N65" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">NarrativeLag, DerateThroughGrowth, CapitalDiscipline, RegimeCyclical, </t>
+          <t>PSIX, NarrativeLag, DerateThroughGrowth, CapitalDiscipline, RegimeCycl</t>
         </is>
       </c>
       <c r="O65" s="24" t="n">
@@ -5960,14 +5960,14 @@
         </is>
       </c>
       <c r="L80" s="22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M80" s="22" t="n">
         <v>4</v>
       </c>
       <c r="N80" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, DerateThroughGrowth, RegimeCyclical, TangibleValue, Owne</t>
+          <t>PSIX, NarrativeLag, DerateThroughGrowth, RegimeCyclical, TangibleValue</t>
         </is>
       </c>
       <c r="O80" s="24" t="n">
@@ -6675,14 +6675,14 @@
         </is>
       </c>
       <c r="L91" s="22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M91" s="22" t="n">
         <v>5</v>
       </c>
       <c r="N91" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, CapitalDiscipline, RegimeCyclical</t>
+          <t>PSIX, NarrativeLag, FixedCost+DemandShock, CapitalDiscipline, RegimeCy</t>
         </is>
       </c>
       <c r="O91" s="24" t="n">
@@ -7256,14 +7256,14 @@
         </is>
       </c>
       <c r="L100" s="22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M100" s="22" t="n">
         <v>5</v>
       </c>
       <c r="N100" s="21" t="inlineStr">
         <is>
-          <t>DerateThroughGrowth, KPIThreshold, ROICInflect, StrongCoverage, BAB-Lo</t>
+          <t>NarrativeLag, DerateThroughGrowth, KPIThreshold, ROICInflect, StrongCo</t>
         </is>
       </c>
       <c r="O100" s="24" t="n">
@@ -8036,14 +8036,14 @@
         </is>
       </c>
       <c r="L112" s="22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M112" s="22" t="n">
         <v>3</v>
       </c>
       <c r="N112" s="21" t="inlineStr">
         <is>
-          <t>DerateThroughGrowth, CashReinvest, CheapPerROIIC, LindyGrowth, Buyback</t>
+          <t>NarrativeLag, DerateThroughGrowth, CashReinvest, CheapPerROIIC, LindyG</t>
         </is>
       </c>
       <c r="O112" s="24" t="n">
@@ -8296,14 +8296,14 @@
         </is>
       </c>
       <c r="L116" s="22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M116" s="22" t="n">
         <v>3</v>
       </c>
       <c r="N116" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, CapitalDiscipline, LargeCapQualit</t>
+          <t>PSIX, NarrativeLag, FixedCost+DemandShock, CapitalDiscipline, LargeCap</t>
         </is>
       </c>
       <c r="O116" s="24" t="n">
@@ -9661,14 +9661,14 @@
         </is>
       </c>
       <c r="L137" s="22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M137" s="22" t="n">
         <v>5</v>
       </c>
       <c r="N137" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, DerateThroughGrowth, FixedCost+DemandShock, KPIThreshold</t>
+          <t>PSIX, NarrativeLag, DerateThroughGrowth, FixedCost+DemandShock, KPIThr</t>
         </is>
       </c>
       <c r="O137" s="24" t="n">
@@ -10303,14 +10303,14 @@
         </is>
       </c>
       <c r="L147" s="22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M147" s="22" t="n">
         <v>3</v>
       </c>
       <c r="N147" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, CapitalDiscipline, ROICInflect, LindyFCF, LargeCapQualit</t>
+          <t>PSIX, NarrativeLag, CapitalDiscipline, ROICInflect, LindyFCF, LargeCap</t>
         </is>
       </c>
       <c r="O147" s="24" t="n">
@@ -10620,14 +10620,14 @@
         </is>
       </c>
       <c r="L152" s="22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M152" s="22" t="n">
         <v>5</v>
       </c>
       <c r="N152" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, DerateThroughGrowth, FixedCost+DemandShock, RegimeCyclic</t>
+          <t>PSIX, NarrativeLag, DerateThroughGrowth, FixedCost+DemandShock, Regime</t>
         </is>
       </c>
       <c r="O152" s="24" t="n">
@@ -11790,14 +11790,14 @@
         </is>
       </c>
       <c r="L170" s="22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M170" s="22" t="n">
         <v>3</v>
       </c>
       <c r="N170" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, DerateThroughGrowth, FixedCost+DemandShock, CapitalDisci</t>
+          <t>PSIX, NarrativeLag, DerateThroughGrowth, FixedCost+DemandShock, Capita</t>
         </is>
       </c>
       <c r="O170" s="24" t="n">
@@ -13988,14 +13988,14 @@
         </is>
       </c>
       <c r="L204" s="22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M204" s="22" t="n">
         <v>3</v>
       </c>
       <c r="N204" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, DeadOption, TangibleValue, BalanceSheetReturn, StrongCov</t>
+          <t>PSIX, NarrativeLag, DeadOption, TangibleValue, BalanceSheetReturn, Str</t>
         </is>
       </c>
       <c r="O204" s="24" t="n">
@@ -15796,14 +15796,14 @@
         </is>
       </c>
       <c r="L232" s="22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M232" s="22" t="n">
         <v>3</v>
       </c>
       <c r="N232" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, DurableReinvest, CheapPerROIIC, N</t>
+          <t>PSIX, NarrativeLag, FixedCost+DemandShock, DurableReinvest, CheapPerRO</t>
         </is>
       </c>
       <c r="O232" s="24" t="n">
@@ -16056,14 +16056,14 @@
         </is>
       </c>
       <c r="L236" s="22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M236" s="22" t="n">
         <v>3</v>
       </c>
       <c r="N236" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">NarrativeLag, DerateThroughGrowth, CapitalDiscipline, RegimeCyclical, </t>
+          <t>PSIX, NarrativeLag, DerateThroughGrowth, CapitalDiscipline, RegimeCycl</t>
         </is>
       </c>
       <c r="O236" s="24" t="n">
@@ -18396,14 +18396,14 @@
         </is>
       </c>
       <c r="L9" s="22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M9" s="22" t="n">
         <v>6</v>
       </c>
       <c r="N9" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, KPIThreshold, ROICInflect, LargeCapQuality, Str</t>
+          <t>PSIX, FixedCost+DemandShock, KPIThreshold, ROICInflect, LargeCapQualit</t>
         </is>
       </c>
       <c r="O9" s="24" t="n">
@@ -20212,14 +20212,14 @@
         </is>
       </c>
       <c r="L37" s="22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M37" s="22" t="n">
         <v>4</v>
       </c>
       <c r="N37" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, DerateThroughGrowth, CashReinvest, LindyMargin, LindyFCF</t>
+          <t>PSIX, NarrativeLag, DerateThroughGrowth, CashReinvest, LindyMargin, Li</t>
         </is>
       </c>
       <c r="O37" s="24" t="n">
@@ -21756,14 +21756,14 @@
         </is>
       </c>
       <c r="L61" s="22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M61" s="22" t="n">
         <v>4</v>
       </c>
       <c r="N61" s="21" t="inlineStr">
         <is>
-          <t>DerateThroughGrowth, CashQuality, MidCapGARP, StrongCoverage, Forensic</t>
+          <t>NarrativeLag, DerateThroughGrowth, CashQuality, MidCapGARP, StrongCove</t>
         </is>
       </c>
       <c r="O61" s="24" t="n">
@@ -26526,14 +26526,14 @@
         </is>
       </c>
       <c r="L135" s="22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M135" s="22" t="n">
         <v>4</v>
       </c>
       <c r="N135" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, DerateThroughGrowth, CashReinvest, LindyMargin, LindyFCF</t>
+          <t>PSIX, NarrativeLag, DerateThroughGrowth, CashReinvest, LindyMargin, Li</t>
         </is>
       </c>
       <c r="O135" s="24" t="n">
@@ -26591,14 +26591,14 @@
         </is>
       </c>
       <c r="L136" s="22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M136" s="22" t="n">
         <v>3</v>
       </c>
       <c r="N136" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, DerateThroughGrowth, DurableReinvest, CashReinvest, Chea</t>
+          <t>PSIX, NarrativeLag, DerateThroughGrowth, DurableReinvest, CashReinvest</t>
         </is>
       </c>
       <c r="O136" s="24" t="n">
@@ -29768,14 +29768,14 @@
         </is>
       </c>
       <c r="L185" s="22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M185" s="22" t="n">
         <v>4</v>
       </c>
       <c r="N185" s="21" t="inlineStr">
         <is>
-          <t>DerateThroughGrowth, KPIThreshold, ROICInflect, DoubleInflect, Capital</t>
+          <t>PSIX, DerateThroughGrowth, KPIThreshold, ROICInflect, DoubleInflect, C</t>
         </is>
       </c>
       <c r="O185" s="24" t="n">
@@ -35159,14 +35159,14 @@
         </is>
       </c>
       <c r="L14" s="22" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M14" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N14" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, DerateThroughGrowth, DeadOption, CheapPerROIIC, LindyMar</t>
+          <t>CheapNetCashSteadyEarner, NarrativeLag, DerateThroughGrowth, DeadOptio</t>
         </is>
       </c>
       <c r="O14" s="24" t="n">
@@ -35744,14 +35744,14 @@
         </is>
       </c>
       <c r="L23" s="22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M23" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N23" s="21" t="inlineStr">
         <is>
-          <t>CapitalDiscipline, OwnerOperator, CashQuality, CapitalReturner, NetCas</t>
+          <t>CheapNetCashSteadyEarner, CapitalDiscipline, OwnerOperator, CashQualit</t>
         </is>
       </c>
       <c r="O23" s="24" t="n">
@@ -36264,14 +36264,14 @@
         </is>
       </c>
       <c r="L31" s="22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M31" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N31" s="21" t="inlineStr">
         <is>
-          <t>DerateThroughGrowth, CapitalDiscipline, OwnerOperator, MidCapGARP, Net</t>
+          <t>PSIX, DerateThroughGrowth, CapitalDiscipline, OwnerOperator, MidCapGAR</t>
         </is>
       </c>
       <c r="O31" s="24" t="n">
@@ -38385,14 +38385,14 @@
         </is>
       </c>
       <c r="L64" s="22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M64" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N64" s="21" t="inlineStr">
         <is>
-          <t>OwnerOperator, Weinstein-Stage2, StrongCoverage, Cluseau-BuybackAccel,</t>
+          <t>NarrativeLag, OwnerOperator, Weinstein-Stage2, StrongCoverage, Cluseau</t>
         </is>
       </c>
       <c r="O64" s="24" t="n">
@@ -39868,14 +39868,14 @@
         </is>
       </c>
       <c r="L87" s="22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M87" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N87" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, CapitalDiscipline, DurableReinvest, CashReinves</t>
+          <t>PSIX, FixedCost+DemandShock, CapitalDiscipline, DurableReinvest, CashR</t>
         </is>
       </c>
       <c r="O87" s="24" t="n">
@@ -42058,14 +42058,14 @@
         </is>
       </c>
       <c r="L121" s="22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M121" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N121" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, DerateThroughGrowth, FixedCost+DemandShock, CapitalDisci</t>
+          <t>PSIX, NarrativeLag, DerateThroughGrowth, FixedCost+DemandShock, Capita</t>
         </is>
       </c>
       <c r="O121" s="24" t="n">
@@ -42968,14 +42968,14 @@
         </is>
       </c>
       <c r="L135" s="22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M135" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N135" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, CapitalDiscipline, DeadOption, DurableReinvest, CashRein</t>
+          <t>PSIX, NarrativeLag, CapitalDiscipline, DeadOption, DurableReinvest, Ca</t>
         </is>
       </c>
       <c r="O135" s="24" t="n">
@@ -43423,14 +43423,14 @@
         </is>
       </c>
       <c r="L142" s="22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M142" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N142" s="21" t="inlineStr">
         <is>
-          <t>FixedCost+DemandShock, CapitalDiscipline, LindyFCF, CapitalLightPivot,</t>
+          <t>NarrativeLag, FixedCost+DemandShock, CapitalDiscipline, LindyFCF, Capi</t>
         </is>
       </c>
       <c r="O142" s="24" t="n">
@@ -46084,14 +46084,14 @@
         </is>
       </c>
       <c r="L183" s="22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M183" s="22" t="n">
         <v>0</v>
       </c>
       <c r="N183" s="21" t="inlineStr">
         <is>
-          <t>DerateThroughGrowth, CapitalDiscipline, DurableReinvest, CheapPerROIIC</t>
+          <t>CheapNetCashSteadyEarner, DerateThroughGrowth, CapitalDiscipline, Dura</t>
         </is>
       </c>
       <c r="O183" s="24" t="n">
@@ -48798,14 +48798,14 @@
         </is>
       </c>
       <c r="L225" s="22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M225" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N225" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, DerateThroughGrowth, DurableReinvest, CashReinvest, Chea</t>
+          <t>PSIX, NarrativeLag, DerateThroughGrowth, DurableReinvest, CashReinvest</t>
         </is>
       </c>
       <c r="O225" s="24" t="n">
@@ -50667,14 +50667,14 @@
         </is>
       </c>
       <c r="L254" s="22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M254" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N254" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, FixedCost+DemandShock, RegimeCyclical, CheapPerROIIC, Re</t>
+          <t>PSIX, NarrativeLag, FixedCost+DemandShock, RegimeCyclical, CheapPerROI</t>
         </is>
       </c>
       <c r="O254" s="24" t="n">
@@ -51252,14 +51252,14 @@
         </is>
       </c>
       <c r="L263" s="22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M263" s="22" t="n">
         <v>1</v>
       </c>
       <c r="N263" s="21" t="inlineStr">
         <is>
-          <t>DerateThroughGrowth, CashReinvest, CheapPerROIIC, CashQuality, LargeCa</t>
+          <t>PSIX, DerateThroughGrowth, CashReinvest, CheapPerROIIC, CashQuality, L</t>
         </is>
       </c>
       <c r="O263" s="24" t="n">
@@ -55518,14 +55518,14 @@
         </is>
       </c>
       <c r="L329" s="22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M329" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N329" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, DerateThroughGrowth, DurableReinvest, CheapPerROIIC, Lin</t>
+          <t>PSIX, NarrativeLag, DerateThroughGrowth, DurableReinvest, CheapPerROII</t>
         </is>
       </c>
       <c r="O329" s="24" t="n">
@@ -56883,14 +56883,14 @@
         </is>
       </c>
       <c r="L350" s="22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M350" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N350" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, DerateThroughGrowth, FixedCost+DemandShock, CheapPerROII</t>
+          <t>PSIX, NarrativeLag, DerateThroughGrowth, FixedCost+DemandShock, CheapP</t>
         </is>
       </c>
       <c r="O350" s="24" t="n">
@@ -57265,14 +57265,14 @@
         </is>
       </c>
       <c r="L356" s="22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M356" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N356" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, DerateThroughGrowth, CapitalDiscipline, LargeCapQuality,</t>
+          <t>PSIX, NarrativeLag, DerateThroughGrowth, CapitalDiscipline, LargeCapQu</t>
         </is>
       </c>
       <c r="O356" s="24" t="n">
@@ -61153,14 +61153,14 @@
         </is>
       </c>
       <c r="L416" s="22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M416" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N416" s="21" t="inlineStr">
         <is>
-          <t>DerateThroughGrowth, FixedCost+DemandShock, KPIThreshold, ROICInflect,</t>
+          <t>PSIX, DerateThroughGrowth, FixedCost+DemandShock, KPIThreshold, ROICIn</t>
         </is>
       </c>
       <c r="O416" s="24" t="n">
@@ -61348,14 +61348,14 @@
         </is>
       </c>
       <c r="L419" s="22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M419" s="22" t="n">
         <v>1</v>
       </c>
       <c r="N419" s="21" t="inlineStr">
         <is>
-          <t>DerateThroughGrowth, CapitalDiscipline, DurableReinvest, CheapPerROIIC</t>
+          <t>NarrativeLag, DerateThroughGrowth, CapitalDiscipline, DurableReinvest,</t>
         </is>
       </c>
       <c r="O419" s="24" t="n">
@@ -61929,14 +61929,14 @@
         </is>
       </c>
       <c r="L428" s="22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M428" s="22" t="n">
         <v>2</v>
       </c>
       <c r="N428" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">NarrativeLag, DurableReinvest, CashReinvest, CheapPerROIIC, LindyFCF, </t>
+          <t>PSIX, NarrativeLag, DurableReinvest, CashReinvest, CheapPerROIIC, Lind</t>
         </is>
       </c>
       <c r="O428" s="24" t="n">
@@ -66471,14 +66471,14 @@
         </is>
       </c>
       <c r="L498" s="22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M498" s="22" t="n">
         <v>0</v>
       </c>
       <c r="N498" s="21" t="inlineStr">
         <is>
-          <t>NarrativeLag, CapitalDiscipline, LindyFCF, NoDilution, BuybackCompound</t>
+          <t>PSIX, NarrativeLag, CapitalDiscipline, LindyFCF, NoDilution, BuybackCo</t>
         </is>
       </c>
       <c r="O498" s="24" t="n">
